--- a/example data/12mm/Results/ID 14 - Run 3/ID 14 - Run 3 - Normalised Stepcycles.xlsx
+++ b/example data/12mm/Results/ID 14 - Run 3/ID 14 - Run 3 - Normalised Stepcycles.xlsx
@@ -666,67 +666,67 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
+          <t>Hind paw tao Velocity</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Acceleration</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Velocity</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Acceleration</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Velocity</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Acceleration</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Velocity</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Acceleration</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Velocity</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Acceleration</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
           <t>Ankle Angle</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Velocity</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Acceleration</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Velocity</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Acceleration</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Velocity</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Acceleration</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Velocity</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Acceleration</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Velocity</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Acceleration</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
@@ -768,34 +768,34 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>304.0204180047867</v>
+        <v>85.5564310195598</v>
       </c>
       <c r="D2" t="n">
-        <v>9.70034497849484</v>
+        <v>9.700344978494847</v>
       </c>
       <c r="E2" t="n">
         <v>0.9959468245506287</v>
       </c>
       <c r="F2" t="n">
-        <v>291.0506410801664</v>
+        <v>72.08106872883249</v>
       </c>
       <c r="G2" t="n">
-        <v>16.13393742987449</v>
+        <v>16.1339374298745</v>
       </c>
       <c r="H2" t="n">
         <v>0.9997597336769104</v>
       </c>
       <c r="I2" t="n">
-        <v>275.2566499912992</v>
+        <v>57.65517417420733</v>
       </c>
       <c r="J2" t="n">
-        <v>1.556948398021945</v>
+        <v>1.556948398021942</v>
       </c>
       <c r="K2" t="n">
         <v>0.9989852607250214</v>
       </c>
       <c r="L2" t="n">
-        <v>272.7424378090716</v>
+        <v>53.96181471804357</v>
       </c>
       <c r="M2" t="n">
         <v>3.486446624106549</v>
@@ -804,7 +804,7 @@
         <v>0.9983863234519958</v>
       </c>
       <c r="O2" t="n">
-        <v>272.461866825185</v>
+        <v>53.35759507848863</v>
       </c>
       <c r="P2" t="n">
         <v>13.33958240265542</v>
@@ -813,7 +813,7 @@
         <v>0.9840632081031799</v>
       </c>
       <c r="R2" t="n">
-        <v>279.1896251921959</v>
+        <v>61.38511008404672</v>
       </c>
       <c r="S2" t="n">
         <v>16.92266261323969</v>
@@ -822,7 +822,7 @@
         <v>0.9901649355888367</v>
       </c>
       <c r="U2" t="n">
-        <v>275.280495907398</v>
+        <v>56.99529647827148</v>
       </c>
       <c r="V2" t="n">
         <v>24.70566769863697</v>
@@ -831,7 +831,7 @@
         <v>0.9891144931316376</v>
       </c>
       <c r="X2" t="n">
-        <v>230.4823246408016</v>
+        <v>13.27799939094706</v>
       </c>
       <c r="Y2" t="n">
         <v>23.77202460106383</v>
@@ -840,7 +840,7 @@
         <v>0.965378999710083</v>
       </c>
       <c r="AA2" t="n">
-        <v>224.9064506368434</v>
+        <v>7.814293719352563</v>
       </c>
       <c r="AB2" t="n">
         <v>17.82310161184758</v>
@@ -849,34 +849,34 @@
         <v>0.8959163725376129</v>
       </c>
       <c r="AD2" t="n">
-        <v>231.2358328636657</v>
+        <v>13.97112176773395</v>
       </c>
       <c r="AE2" t="n">
-        <v>10.19727828654838</v>
+        <v>10.19727828654837</v>
       </c>
       <c r="AF2" t="n">
         <v>0.9590792953968048</v>
       </c>
       <c r="AG2" t="n">
-        <v>221.3638630319149</v>
+        <v>3.554348235434674</v>
       </c>
       <c r="AH2" t="n">
-        <v>13.58552486338515</v>
+        <v>13.58552486338514</v>
       </c>
       <c r="AI2" t="n">
         <v>0.9726399183273315</v>
       </c>
       <c r="AJ2" t="n">
-        <v>221.1754453943131</v>
+        <v>3.264962865951205</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.381683349609389</v>
+        <v>1.381683349609375</v>
       </c>
       <c r="AL2" t="n">
         <v>0.9967140555381775</v>
       </c>
       <c r="AM2" t="n">
-        <v>212.643736981331</v>
+        <v>-5.662175442310101</v>
       </c>
       <c r="AN2" t="n">
         <v>16.3762924518991</v>
@@ -885,7 +885,7 @@
         <v>0.9997424781322479</v>
       </c>
       <c r="AP2" t="n">
-        <v>175.2889024450424</v>
+        <v>-42.14157753802361</v>
       </c>
       <c r="AQ2" t="n">
         <v>27.1120030829247</v>
@@ -894,70 +894,70 @@
         <v>0.9435849189758301</v>
       </c>
       <c r="AS2" t="n">
-        <v>137.6906618158868</v>
+        <v>-80.07905026699635</v>
       </c>
       <c r="AT2" t="n">
-        <v>38.96923471004406</v>
+        <v>38.96923471004405</v>
       </c>
       <c r="AU2" t="n">
         <v>0.9936793446540833</v>
       </c>
       <c r="AV2" t="n">
-        <v>71.57315439480445</v>
+        <v>6.063737260534396</v>
       </c>
       <c r="AW2" t="n">
-        <v>31.59051981959138</v>
+        <v>-0.9354195696242193</v>
       </c>
       <c r="AX2" t="n">
-        <v>97.35079972189557</v>
+        <v>2.87665914981924</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.063737260534417</v>
+        <v>-0.2685090328784874</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.9354195696242371</v>
+        <v>3.398349437307807</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.876659149819226</v>
+        <v>-0.01310186183198425</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.2685090328784661</v>
+        <v>1.645948531779837</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.398349437307822</v>
+        <v>0.3480951836768504</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01310186183200557</v>
+        <v>1.384473354258425</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.645948531779844</v>
+        <v>0.6225301864299411</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.3480951836768611</v>
+        <v>72.95426273796947</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.384473354258439</v>
+        <v>33.27895452987493</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.6225301864299162</v>
+        <v>98.7053093251463</v>
       </c>
       <c r="BI2" t="n">
-        <v>-5.574897892447495</v>
+        <v>-5.994826976693538</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3.06189646368513</v>
+        <v>2.939184202646842</v>
       </c>
       <c r="BK2" t="n">
-        <v>-1.297187821898929</v>
+        <v>-1.923409097708214</v>
       </c>
       <c r="BL2" t="n">
-        <v>2.503904333851514</v>
+        <v>2.423172225482075</v>
       </c>
       <c r="BM2" t="n">
-        <v>-10.15878880860162</v>
+        <v>-10.29878530832085</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.54551368393278</v>
+        <v>1.532912405434711</v>
       </c>
     </row>
     <row r="3">
@@ -968,16 +968,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>306.2289932940869</v>
+        <v>87.76500630885997</v>
       </c>
       <c r="D3" t="n">
-        <v>10.08987426757811</v>
+        <v>10.08987426757812</v>
       </c>
       <c r="E3" t="n">
         <v>0.9969565868377686</v>
       </c>
       <c r="F3" t="n">
-        <v>293.1282986985876</v>
+        <v>74.15872634725369</v>
       </c>
       <c r="G3" t="n">
         <v>16.2890170482879</v>
@@ -986,25 +986,25 @@
         <v>0.9996919333934784</v>
       </c>
       <c r="I3" t="n">
-        <v>275.2354479850607</v>
+        <v>57.63397216796875</v>
       </c>
       <c r="J3" t="n">
-        <v>1.684075213493188</v>
+        <v>1.684075213493185</v>
       </c>
       <c r="K3" t="n">
         <v>0.9988817572593689</v>
       </c>
       <c r="L3" t="n">
-        <v>272.9336474804168</v>
+        <v>54.15302438938872</v>
       </c>
       <c r="M3" t="n">
-        <v>3.680533551155236</v>
+        <v>3.680533551155253</v>
       </c>
       <c r="N3" t="n">
         <v>0.9985505640506744</v>
       </c>
       <c r="O3" t="n">
-        <v>274.5087501850534</v>
+        <v>55.40447843835707</v>
       </c>
       <c r="P3" t="n">
         <v>13.59830815741356</v>
@@ -1013,16 +1013,16 @@
         <v>0.9831846356391907</v>
       </c>
       <c r="R3" t="n">
-        <v>281.1916148408931</v>
+        <v>63.38709973274393</v>
       </c>
       <c r="S3" t="n">
-        <v>16.90899463410074</v>
+        <v>16.90899463410073</v>
       </c>
       <c r="T3" t="n">
         <v>0.9929656088352203</v>
       </c>
       <c r="U3" t="n">
-        <v>277.6675183722314</v>
+        <v>59.38231894310485</v>
       </c>
       <c r="V3" t="n">
         <v>24.40801579901512</v>
@@ -1031,34 +1031,34 @@
         <v>0.9906905293464661</v>
       </c>
       <c r="X3" t="n">
-        <v>234.1130926253948</v>
+        <v>16.90876737554022</v>
       </c>
       <c r="Y3" t="n">
-        <v>24.11592361774849</v>
+        <v>24.11592361774851</v>
       </c>
       <c r="Z3" t="n">
         <v>0.9703371524810791</v>
       </c>
       <c r="AA3" t="n">
-        <v>228.7539786480843</v>
+        <v>11.6618217305934</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.5148659564079</v>
+        <v>17.51486595640791</v>
       </c>
       <c r="AC3" t="n">
         <v>0.9572224915027618</v>
       </c>
       <c r="AD3" t="n">
-        <v>237.7481338825632</v>
+        <v>20.48342278663148</v>
       </c>
       <c r="AE3" t="n">
-        <v>12.10574697940906</v>
+        <v>12.10574697940908</v>
       </c>
       <c r="AF3" t="n">
         <v>0.9679689109325409</v>
       </c>
       <c r="AG3" t="n">
-        <v>226.6667264573118</v>
+        <v>8.857211660831524</v>
       </c>
       <c r="AH3" t="n">
         <v>11.36017657340841</v>
@@ -1067,97 +1067,97 @@
         <v>0.9842641651630402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>231.425995522357</v>
+        <v>13.51551299399517</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.277203823657743</v>
+        <v>2.277203823657746</v>
       </c>
       <c r="AL3" t="n">
         <v>0.9979981184005737</v>
       </c>
       <c r="AM3" t="n">
-        <v>215.4158287859977</v>
+        <v>-2.890083637643372</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.1835122615733</v>
+        <v>16.18351226157331</v>
       </c>
       <c r="AO3" t="n">
         <v>0.9995158612728119</v>
       </c>
       <c r="AP3" t="n">
-        <v>178.2412833355843</v>
+        <v>-39.18919664748172</v>
       </c>
       <c r="AQ3" t="n">
-        <v>27.72229783078456</v>
+        <v>27.72229783078458</v>
       </c>
       <c r="AR3" t="n">
         <v>0.9358174800872803</v>
       </c>
       <c r="AS3" t="n">
-        <v>140.0895707150723</v>
+        <v>-77.68014136781085</v>
       </c>
       <c r="AT3" t="n">
-        <v>40.58680838726936</v>
+        <v>40.58680838726937</v>
       </c>
       <c r="AU3" t="n">
         <v>0.997650682926178</v>
       </c>
       <c r="AV3" t="n">
-        <v>65.92014666552413</v>
+        <v>4.347655113707205</v>
       </c>
       <c r="AW3" t="n">
-        <v>34.9342036269334</v>
+        <v>-0.7612258829969036</v>
       </c>
       <c r="AX3" t="n">
-        <v>82.02695181074209</v>
+        <v>2.716291711685507</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.347655113707198</v>
+        <v>-0.0889209990805746</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.7612258829969036</v>
+        <v>2.659128067341257</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.7162917116855</v>
+        <v>-0.5334823689562214</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.0889209990805746</v>
+        <v>2.030865689541429</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.659128067341257</v>
+        <v>0.03694879247787952</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.5334823689562249</v>
+        <v>1.77966584550574</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.030865689541429</v>
+        <v>0.005236077815929718</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.03694879247786531</v>
+        <v>66.23265085629151</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.77966584550574</v>
+        <v>35.24687161100125</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.005236077815940376</v>
+        <v>83.11102069611736</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.06521194272693975</v>
+        <v>-0.6655717684039324</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.697425392699827</v>
+        <v>1.702087663963328</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.635885726770332</v>
+        <v>4.952211269385909</v>
       </c>
       <c r="BL3" t="n">
-        <v>2.567379063011932</v>
+        <v>2.63910556758429</v>
       </c>
       <c r="BM3" t="n">
-        <v>-4.470789076382481</v>
+        <v>-4.546850062089387</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.851613531139311</v>
+        <v>1.896360062281039</v>
       </c>
     </row>
     <row r="4">
@@ -1168,43 +1168,43 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>308.8476662940167</v>
+        <v>90.38367930878985</v>
       </c>
       <c r="D4" t="n">
-        <v>11.37162878158244</v>
+        <v>11.37162878158245</v>
       </c>
       <c r="E4" t="n">
         <v>0.9985638558864594</v>
       </c>
       <c r="F4" t="n">
-        <v>295.1351216498842</v>
+        <v>76.16554929855022</v>
       </c>
       <c r="G4" t="n">
-        <v>16.78559323574633</v>
+        <v>16.78559323574634</v>
       </c>
       <c r="H4" t="n">
         <v>0.9996896684169769</v>
       </c>
       <c r="I4" t="n">
-        <v>275.3230723928898</v>
+        <v>57.72159657579786</v>
       </c>
       <c r="J4" t="n">
-        <v>1.729121106736201</v>
+        <v>1.729121106736204</v>
       </c>
       <c r="K4" t="n">
         <v>0.9991251826286316</v>
       </c>
       <c r="L4" t="n">
-        <v>273.1205108317923</v>
+        <v>54.3398877407642</v>
       </c>
       <c r="M4" t="n">
-        <v>3.753970531707111</v>
+        <v>3.753970531707115</v>
       </c>
       <c r="N4" t="n">
         <v>0.9984859824180603</v>
       </c>
       <c r="O4" t="n">
-        <v>276.4780490956408</v>
+        <v>57.37377734894446</v>
       </c>
       <c r="P4" t="n">
         <v>13.58752149216672</v>
@@ -1213,7 +1213,7 @@
         <v>0.9834736883640289</v>
       </c>
       <c r="R4" t="n">
-        <v>283.1692553581076</v>
+        <v>65.36474024995846</v>
       </c>
       <c r="S4" t="n">
         <v>16.97200207000083</v>
@@ -1222,16 +1222,16 @@
         <v>0.9906691312789917</v>
       </c>
       <c r="U4" t="n">
-        <v>279.1994723867863</v>
+        <v>60.91427295765979</v>
       </c>
       <c r="V4" t="n">
-        <v>24.33477361151512</v>
+        <v>24.33477361151513</v>
       </c>
       <c r="W4" t="n">
         <v>0.990548312664032</v>
       </c>
       <c r="X4" t="n">
-        <v>237.7648049212517</v>
+        <v>20.5604796713971</v>
       </c>
       <c r="Y4" t="n">
         <v>24.27717979918135</v>
@@ -1240,7 +1240,7 @@
         <v>0.9590609669685364</v>
       </c>
       <c r="AA4" t="n">
-        <v>232.7493018292366</v>
+        <v>15.65714491174576</v>
       </c>
       <c r="AB4" t="n">
         <v>17.74899908836852</v>
@@ -1249,34 +1249,34 @@
         <v>0.9767678678035736</v>
       </c>
       <c r="AD4" t="n">
-        <v>242.1265054256359</v>
+        <v>24.86179432970413</v>
       </c>
       <c r="AE4" t="n">
-        <v>14.03792360995679</v>
+        <v>14.03792360995678</v>
       </c>
       <c r="AF4" t="n">
         <v>0.9232169389724731</v>
       </c>
       <c r="AG4" t="n">
-        <v>231.6139058863863</v>
+        <v>13.80439108990608</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.660466620262639</v>
+        <v>8.660466620262632</v>
       </c>
       <c r="AI4" t="n">
         <v>0.9931458532810211</v>
       </c>
       <c r="AJ4" t="n">
-        <v>238.6316421184134</v>
+        <v>20.72115959005153</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.771393796230882</v>
+        <v>2.771393796230885</v>
       </c>
       <c r="AL4" t="n">
         <v>0.9987861514091492</v>
       </c>
       <c r="AM4" t="n">
-        <v>217.9927907091506</v>
+        <v>-0.3131217144905349</v>
       </c>
       <c r="AN4" t="n">
         <v>16.18119909408244</v>
@@ -1285,7 +1285,7 @@
         <v>0.9992123246192932</v>
       </c>
       <c r="AP4" t="n">
-        <v>180.8052631134682</v>
+        <v>-36.62521686959774</v>
       </c>
       <c r="AQ4" t="n">
         <v>29.54567036730178</v>
@@ -1294,7 +1294,7 @@
         <v>0.8980639576911926</v>
       </c>
       <c r="AS4" t="n">
-        <v>144.4485035348446</v>
+        <v>-73.32120854803857</v>
       </c>
       <c r="AT4" t="n">
         <v>44.67603805217338</v>
@@ -1303,61 +1303,61 @@
         <v>0.9943361878395081</v>
       </c>
       <c r="AV4" t="n">
-        <v>67.05684050704312</v>
+        <v>3.313776787291182</v>
       </c>
       <c r="AW4" t="n">
-        <v>48.54740368632315</v>
+        <v>-0.02885067716558254</v>
       </c>
       <c r="AX4" t="n">
-        <v>74.10955802414585</v>
+        <v>2.376461029052734</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.313776787291175</v>
+        <v>0.237091551435757</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.02885067716558254</v>
+        <v>1.978969573974609</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.376461029052741</v>
+        <v>-0.2373604064292145</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.2370915514357534</v>
+        <v>1.692140863296835</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.978969573974602</v>
+        <v>-0.2351679700486251</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.2373604064292074</v>
+        <v>1.580197760399351</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.692140863296835</v>
+        <v>-0.276820203091237</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.2351679700486144</v>
+        <v>66.31938963046687</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.580197760399351</v>
+        <v>47.77121096246473</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.2768202030912512</v>
+        <v>75.10217231621257</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0.6524974445439291</v>
+        <v>-1.084084710458072</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.01168091753865852</v>
+        <v>0.02842645294153456</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.209887781645275</v>
+        <v>5.798242513085203</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.07362792849637501</v>
+        <v>0.1391900760839322</v>
       </c>
       <c r="BM4" t="n">
-        <v>-2.357653522392251</v>
+        <v>-2.413957945176442</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.030927782702525</v>
+        <v>2.029544614487405</v>
       </c>
     </row>
     <row r="5">
@@ -1368,16 +1368,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>310.7890590708307</v>
+        <v>92.32507208560375</v>
       </c>
       <c r="D5" t="n">
-        <v>12.57427296739942</v>
+        <v>12.57427296739943</v>
       </c>
       <c r="E5" t="n">
         <v>0.9986657202243805</v>
       </c>
       <c r="F5" t="n">
-        <v>296.9983811074115</v>
+        <v>78.02880875607752</v>
       </c>
       <c r="G5" t="n">
         <v>17.11814555716008</v>
@@ -1386,178 +1386,178 @@
         <v>0.9993353486061096</v>
       </c>
       <c r="I5" t="n">
-        <v>275.4180502384267</v>
+        <v>57.81657442133479</v>
       </c>
       <c r="J5" t="n">
-        <v>1.674278746259972</v>
+        <v>1.674278746259974</v>
       </c>
       <c r="K5" t="n">
         <v>0.9993556141853333</v>
       </c>
       <c r="L5" t="n">
-        <v>273.3812900299721</v>
+        <v>54.60066693894404</v>
       </c>
       <c r="M5" t="n">
-        <v>3.919000828519785</v>
+        <v>3.919000828519781</v>
       </c>
       <c r="N5" t="n">
         <v>0.9983317255973816</v>
       </c>
       <c r="O5" t="n">
-        <v>277.694649391986</v>
+        <v>58.59037764528964</v>
       </c>
       <c r="P5" t="n">
-        <v>13.68380607442651</v>
+        <v>13.68380607442653</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9895745515823364</v>
       </c>
       <c r="R5" t="n">
-        <v>284.1122647549244</v>
+        <v>66.30774964677528</v>
       </c>
       <c r="S5" t="n">
-        <v>17.1012391435339</v>
+        <v>17.10123914353391</v>
       </c>
       <c r="T5" t="n">
         <v>0.9902363717556</v>
       </c>
       <c r="U5" t="n">
-        <v>280.9233259647451</v>
+        <v>62.63812653561857</v>
       </c>
       <c r="V5" t="n">
-        <v>24.33694068421708</v>
+        <v>24.33694068421709</v>
       </c>
       <c r="W5" t="n">
         <v>0.9916018843650818</v>
       </c>
       <c r="X5" t="n">
-        <v>240.3092364047436</v>
+        <v>23.10491115488904</v>
       </c>
       <c r="Y5" t="n">
-        <v>24.93356745293798</v>
+        <v>24.933567452938</v>
       </c>
       <c r="Z5" t="n">
         <v>0.9575487971305847</v>
       </c>
       <c r="AA5" t="n">
-        <v>235.8039531301945</v>
+        <v>18.71179621270362</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.42836972500415</v>
+        <v>17.42836972500416</v>
       </c>
       <c r="AC5" t="n">
         <v>0.9776656627655029</v>
       </c>
       <c r="AD5" t="n">
-        <v>245.5554353429916</v>
+        <v>28.29072424705991</v>
       </c>
       <c r="AE5" t="n">
-        <v>14.76079250903838</v>
+        <v>14.7607925090384</v>
       </c>
       <c r="AF5" t="n">
         <v>0.8957958519458771</v>
       </c>
       <c r="AG5" t="n">
-        <v>237.5094515212039</v>
+        <v>19.69993672472366</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.061302347386132</v>
+        <v>6.061302347386137</v>
       </c>
       <c r="AI5" t="n">
         <v>0.9947902858257294</v>
       </c>
       <c r="AJ5" t="n">
-        <v>245.7218860058074</v>
+        <v>27.81140347744555</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.925036815886799</v>
+        <v>2.925036815886802</v>
       </c>
       <c r="AL5" t="n">
         <v>0.9990834891796112</v>
       </c>
       <c r="AM5" t="n">
-        <v>221.1060544277759</v>
+        <v>2.800142004134798</v>
       </c>
       <c r="AN5" t="n">
-        <v>16.50624376662233</v>
+        <v>16.50624376662234</v>
       </c>
       <c r="AO5" t="n">
         <v>0.9996916055679321</v>
       </c>
       <c r="AP5" t="n">
-        <v>184.6861129111432</v>
+        <v>-32.7443670719228</v>
       </c>
       <c r="AQ5" t="n">
-        <v>31.10082504597115</v>
+        <v>31.10082504597116</v>
       </c>
       <c r="AR5" t="n">
         <v>0.8998968005180359</v>
       </c>
       <c r="AS5" t="n">
-        <v>148.9259192284117</v>
+        <v>-68.84379285447142</v>
       </c>
       <c r="AT5" t="n">
-        <v>48.58968612995553</v>
+        <v>48.58968612995554</v>
       </c>
       <c r="AU5" t="n">
         <v>0.9952656030654907</v>
       </c>
       <c r="AV5" t="n">
-        <v>68.14681067840748</v>
+        <v>3.40811952631524</v>
       </c>
       <c r="AW5" t="n">
-        <v>62.4551154596984</v>
+        <v>-0.1391076027078775</v>
       </c>
       <c r="AX5" t="n">
-        <v>74.31587536835971</v>
+        <v>2.882908760233128</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.408119526315247</v>
+        <v>-0.2279819326197874</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.139107602707881</v>
+        <v>1.64816836093334</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.882908760233121</v>
+        <v>0.05897664009257042</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.2279819326197838</v>
+        <v>1.728486000223363</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.648168360933354</v>
+        <v>0.2037322267572925</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.05897664009257042</v>
+        <v>1.457285373768904</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.728486000223363</v>
+        <v>0.09350472308220148</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.2037322267572925</v>
+        <v>66.51983421640836</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.457285373768897</v>
+        <v>60.85231061826394</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.09350472308220859</v>
+        <v>75.21150239425742</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.004066316748527754</v>
+        <v>-0.3595308265706141</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.9644195331155281</v>
+        <v>-0.8359001894697355</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.562612580488619</v>
+        <v>6.272296476584847</v>
       </c>
       <c r="BL5" t="n">
-        <v>-1.633680077475893</v>
+        <v>-1.489877437939967</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.609417603904561</v>
+        <v>1.599516424628884</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.441464631343907</v>
+        <v>1.472165985431319</v>
       </c>
     </row>
     <row r="6">
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>312.2983425221545</v>
+        <v>93.83435553692755</v>
       </c>
       <c r="D6" t="n">
         <v>12.78519326067985</v>
@@ -1577,7 +1577,7 @@
         <v>0.996954083442688</v>
       </c>
       <c r="F6" t="n">
-        <v>298.5368383691666</v>
+        <v>79.56726601783265</v>
       </c>
       <c r="G6" t="n">
         <v>17.77914331314412</v>
@@ -1586,34 +1586,34 @@
         <v>0.999398946762085</v>
       </c>
       <c r="I6" t="n">
-        <v>275.5397045865972</v>
+        <v>57.93822876950529</v>
       </c>
       <c r="J6" t="n">
-        <v>2.019525081553354</v>
+        <v>2.019525081553358</v>
       </c>
       <c r="K6" t="n">
         <v>0.9992599189281464</v>
       </c>
       <c r="L6" t="n">
-        <v>273.9479470760264</v>
+        <v>55.16732398499835</v>
       </c>
       <c r="M6" t="n">
-        <v>4.325663789789729</v>
+        <v>4.325663789789727</v>
       </c>
       <c r="N6" t="n">
         <v>0.9967128336429596</v>
       </c>
       <c r="O6" t="n">
-        <v>278.4689700349849</v>
+        <v>59.36469828828851</v>
       </c>
       <c r="P6" t="n">
-        <v>14.62643400151678</v>
+        <v>14.62643400151679</v>
       </c>
       <c r="Q6" t="n">
         <v>0.9891950190067291</v>
       </c>
       <c r="R6" t="n">
-        <v>285.6709257085273</v>
+        <v>67.86641060037815</v>
       </c>
       <c r="S6" t="n">
         <v>17.75972082259807</v>
@@ -1622,7 +1622,7 @@
         <v>0.9939253926277161</v>
       </c>
       <c r="U6" t="n">
-        <v>282.0529105815482</v>
+        <v>63.76771115242167</v>
       </c>
       <c r="V6" t="n">
         <v>25.27665483190658</v>
@@ -1631,16 +1631,16 @@
         <v>0.989942729473114</v>
       </c>
       <c r="X6" t="n">
-        <v>243.2276867805643</v>
+        <v>26.02336153070978</v>
       </c>
       <c r="Y6" t="n">
-        <v>24.876971954995</v>
+        <v>24.87697195499501</v>
       </c>
       <c r="Z6" t="n">
         <v>0.9614523947238922</v>
       </c>
       <c r="AA6" t="n">
-        <v>239.6735333381815</v>
+        <v>22.58137642069065</v>
       </c>
       <c r="AB6" t="n">
         <v>16.86432209420711</v>
@@ -1649,7 +1649,7 @@
         <v>0.9810217022895813</v>
       </c>
       <c r="AD6" t="n">
-        <v>249.2202718207177</v>
+        <v>31.95556072478598</v>
       </c>
       <c r="AE6" t="n">
         <v>14.45136374615608</v>
@@ -1658,106 +1658,106 @@
         <v>0.9084337949752808</v>
       </c>
       <c r="AG6" t="n">
-        <v>242.4930694255423</v>
+        <v>24.68355462906209</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.588488315014118</v>
+        <v>4.588488315014129</v>
       </c>
       <c r="AI6" t="n">
         <v>0.9888662695884705</v>
       </c>
       <c r="AJ6" t="n">
-        <v>252.2556994823699</v>
+        <v>34.34521695400807</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.929395310422194</v>
+        <v>2.929395310422207</v>
       </c>
       <c r="AL6" t="n">
         <v>0.9994131326675415</v>
       </c>
       <c r="AM6" t="n">
-        <v>223.6582167605137</v>
+        <v>5.352304336872507</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.75216739735704</v>
+        <v>15.75216739735705</v>
       </c>
       <c r="AO6" t="n">
         <v>0.9996267259120941</v>
       </c>
       <c r="AP6" t="n">
-        <v>188.0720260295462</v>
+        <v>-29.3584539535198</v>
       </c>
       <c r="AQ6" t="n">
-        <v>30.8894948756441</v>
+        <v>30.88949487564412</v>
       </c>
       <c r="AR6" t="n">
         <v>0.8544211685657501</v>
       </c>
       <c r="AS6" t="n">
-        <v>152.8323072068235</v>
+        <v>-64.93740487605969</v>
       </c>
       <c r="AT6" t="n">
-        <v>48.7466812133789</v>
+        <v>48.74668121337891</v>
       </c>
       <c r="AU6" t="n">
         <v>0.9956978857517242</v>
       </c>
       <c r="AV6" t="n">
-        <v>65.37910271730972</v>
+        <v>3.218692414304051</v>
       </c>
       <c r="AW6" t="n">
-        <v>69.82810692317008</v>
+        <v>-0.1431044111860622</v>
       </c>
       <c r="AX6" t="n">
-        <v>80.28805123794922</v>
+        <v>2.551799124859748</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.218692414304044</v>
+        <v>0.1270831899440026</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.1431044111860587</v>
+        <v>1.84151061037754</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.551799124859755</v>
+        <v>-0.01290301059154686</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.1270831899440061</v>
+        <v>1.912731819964471</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.841510610377533</v>
+        <v>-0.05036719301913095</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.01290301059155752</v>
+        <v>1.308851039156004</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.912731819964471</v>
+        <v>0.01465208986971689</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.05036719301914161</v>
+        <v>63.37667804447091</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.308851039156011</v>
+        <v>67.97390052230327</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.01465208986972044</v>
+        <v>81.20949641402753</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.465264975514696</v>
+        <v>1.351063580827345</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2.802750743925008</v>
+        <v>2.854541060319823</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.992611972234894</v>
+        <v>2.893131493848404</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.3424769832851684</v>
+        <v>0.360534902591775</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.507255271674911</v>
+        <v>2.506661957696267</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.879252514304989</v>
+        <v>-0.8986240233899174</v>
       </c>
     </row>
     <row r="7">
@@ -1768,52 +1768,52 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>314.123767741183</v>
+        <v>95.65978075595612</v>
       </c>
       <c r="D7" t="n">
-        <v>13.27375046750332</v>
+        <v>13.27375046750333</v>
       </c>
       <c r="E7" t="n">
         <v>0.9953908026218414</v>
       </c>
       <c r="F7" t="n">
-        <v>300.2009310620897</v>
+        <v>81.2313587107557</v>
       </c>
       <c r="G7" t="n">
-        <v>18.2031347396526</v>
+        <v>18.20313473965259</v>
       </c>
       <c r="H7" t="n">
         <v>0.9987646341323853</v>
       </c>
       <c r="I7" t="n">
-        <v>276.0714794727082</v>
+        <v>58.47000365561627</v>
       </c>
       <c r="J7" t="n">
-        <v>2.017163215799513</v>
+        <v>2.017163215799535</v>
       </c>
       <c r="K7" t="n">
         <v>0.9988489151000977</v>
       </c>
       <c r="L7" t="n">
-        <v>274.2025943512612</v>
+        <v>55.42197126023311</v>
       </c>
       <c r="M7" t="n">
-        <v>4.584016191198472</v>
+        <v>4.58401619119847</v>
       </c>
       <c r="N7" t="n">
         <v>0.9936686456203461</v>
       </c>
       <c r="O7" t="n">
-        <v>279.85712619538</v>
+        <v>60.75285444868371</v>
       </c>
       <c r="P7" t="n">
-        <v>14.76609250332446</v>
+        <v>14.76609250332447</v>
       </c>
       <c r="Q7" t="n">
         <v>0.9844550788402557</v>
       </c>
       <c r="R7" t="n">
-        <v>287.2817729381805</v>
+        <v>69.47725783003136</v>
       </c>
       <c r="S7" t="n">
         <v>18.27546789291057</v>
@@ -1822,25 +1822,25 @@
         <v>0.9919746518135071</v>
       </c>
       <c r="U7" t="n">
-        <v>283.7388119799026</v>
+        <v>65.45361255077603</v>
       </c>
       <c r="V7" t="n">
-        <v>25.53785202351021</v>
+        <v>25.53785202351023</v>
       </c>
       <c r="W7" t="n">
         <v>0.98531174659729</v>
       </c>
       <c r="X7" t="n">
-        <v>246.2047455158639</v>
+        <v>29.00042026600939</v>
       </c>
       <c r="Y7" t="n">
-        <v>25.7169155364341</v>
+        <v>25.71691553643409</v>
       </c>
       <c r="Z7" t="n">
         <v>0.9643067121505737</v>
       </c>
       <c r="AA7" t="n">
-        <v>243.341644774092</v>
+        <v>26.24948785660115</v>
       </c>
       <c r="AB7" t="n">
         <v>17.03455498877992</v>
@@ -1849,144 +1849,144 @@
         <v>0.9484047293663025</v>
       </c>
       <c r="AD7" t="n">
-        <v>252.8334962560776</v>
+        <v>35.56878516014586</v>
       </c>
       <c r="AE7" t="n">
-        <v>15.19116340799533</v>
+        <v>15.19116340799535</v>
       </c>
       <c r="AF7" t="n">
         <v>0.963498592376709</v>
       </c>
       <c r="AG7" t="n">
-        <v>247.9850200896568</v>
+        <v>30.17550529317653</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.442350346991347</v>
+        <v>3.442350346991357</v>
       </c>
       <c r="AI7" t="n">
         <v>0.9934154152870178</v>
       </c>
       <c r="AJ7" t="n">
-        <v>258.2170953141882</v>
+        <v>40.30661278582633</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.315764731549194</v>
+        <v>2.315764731549202</v>
       </c>
       <c r="AL7" t="n">
         <v>0.9990601241588593</v>
       </c>
       <c r="AM7" t="n">
-        <v>226.5367102115712</v>
+        <v>8.230797787930101</v>
       </c>
       <c r="AN7" t="n">
-        <v>15.08413274237451</v>
+        <v>15.0841327423745</v>
       </c>
       <c r="AO7" t="n">
         <v>0.9992314577102661</v>
       </c>
       <c r="AP7" t="n">
-        <v>191.5513951727685</v>
+        <v>-25.87908481029754</v>
       </c>
       <c r="AQ7" t="n">
-        <v>29.80905086436169</v>
+        <v>29.8090508643617</v>
       </c>
       <c r="AR7" t="n">
         <v>0.8627478778362274</v>
       </c>
       <c r="AS7" t="n">
-        <v>155.8797714558053</v>
+        <v>-61.88994062707781</v>
       </c>
       <c r="AT7" t="n">
-        <v>48.20667834992104</v>
+        <v>48.20667834992105</v>
       </c>
       <c r="AU7" t="n">
         <v>0.9941371381282806</v>
       </c>
       <c r="AV7" t="n">
-        <v>73.82239773191199</v>
+        <v>2.524545344900559</v>
       </c>
       <c r="AW7" t="n">
-        <v>78.57100631978244</v>
+        <v>-0.7646839669410213</v>
       </c>
       <c r="AX7" t="n">
-        <v>82.74321705031875</v>
+        <v>2.856009057227602</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.524545344900574</v>
+        <v>-0.2201587595838177</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.7646839669410141</v>
+        <v>1.977098749039023</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.856009057227602</v>
+        <v>-0.01329665488385245</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.2201587595838177</v>
+        <v>1.861769087771151</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.977098749039016</v>
+        <v>-0.1045947379254351</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.01329665488384535</v>
+        <v>1.628542960958278</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.861769087771151</v>
+        <v>0.01230950051165891</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1045947379254244</v>
+        <v>71.65168611381274</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.628542960958278</v>
+        <v>76.53763003670971</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.01230950051165891</v>
+        <v>83.61299434023798</v>
       </c>
       <c r="BI7" t="n">
-        <v>5.514745026814101</v>
+        <v>5.488513375480629</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.9003689724169526</v>
+        <v>0.9402637477250932</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.023367208624379</v>
+        <v>3.968267018558233</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.4146132359576153</v>
+        <v>-0.3878389324823424</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.248306763294533</v>
+        <v>1.210463529984899</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.4626156862679629</v>
+        <v>0.4798802638041266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6.765</v>
+        <v>6.765000000000001</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>316.3510255357052</v>
+        <v>97.88703855047834</v>
       </c>
       <c r="D8" t="n">
-        <v>14.43593451317321</v>
+        <v>14.4359345131732</v>
       </c>
       <c r="E8" t="n">
         <v>0.9967568516731262</v>
       </c>
       <c r="F8" t="n">
-        <v>302.5329214461307</v>
+        <v>83.56334909479668</v>
       </c>
       <c r="G8" t="n">
-        <v>18.90710871270362</v>
+        <v>18.90710871270363</v>
       </c>
       <c r="H8" t="n">
         <v>0.9989941716194153</v>
       </c>
       <c r="I8" t="n">
-        <v>276.5013857090727</v>
+        <v>58.89990989198074</v>
       </c>
       <c r="J8" t="n">
         <v>1.6510009765625</v>
@@ -1995,16 +1995,16 @@
         <v>0.9991049468517303</v>
       </c>
       <c r="L8" t="n">
-        <v>275.3125393644292</v>
+        <v>56.53191627340112</v>
       </c>
       <c r="M8" t="n">
-        <v>5.093205228764958</v>
+        <v>5.09320522876496</v>
       </c>
       <c r="N8" t="n">
         <v>0.9923620820045471</v>
       </c>
       <c r="O8" t="n">
-        <v>281.5855513227747</v>
+        <v>62.48127957607835</v>
       </c>
       <c r="P8" t="n">
         <v>14.91807978203956</v>
@@ -2013,16 +2013,16 @@
         <v>0.9907947480678558</v>
       </c>
       <c r="R8" t="n">
-        <v>288.8131719954471</v>
+        <v>71.00865688729792</v>
       </c>
       <c r="S8" t="n">
-        <v>17.90182235393118</v>
+        <v>17.90182235393119</v>
       </c>
       <c r="T8" t="n">
         <v>0.9922588467597961</v>
       </c>
       <c r="U8" t="n">
-        <v>285.5492957094883</v>
+        <v>67.26409628036174</v>
       </c>
       <c r="V8" t="n">
         <v>25.5456843274705</v>
@@ -2031,7 +2031,7 @@
         <v>0.9886278808116913</v>
       </c>
       <c r="X8" t="n">
-        <v>249.2310422532102</v>
+        <v>32.02671700335563</v>
       </c>
       <c r="Y8" t="n">
         <v>26.43678949234334</v>
@@ -2040,7 +2040,7 @@
         <v>0.968449592590332</v>
       </c>
       <c r="AA8" t="n">
-        <v>246.5913772583008</v>
+        <v>29.49922034080991</v>
       </c>
       <c r="AB8" t="n">
         <v>17.40388261510971</v>
@@ -2049,7 +2049,7 @@
         <v>0.9569335877895355</v>
       </c>
       <c r="AD8" t="n">
-        <v>256.3935340719021</v>
+        <v>39.12882297597034</v>
       </c>
       <c r="AE8" t="n">
         <v>15.07430380963265</v>
@@ -2058,25 +2058,25 @@
         <v>0.9831895232200623</v>
       </c>
       <c r="AG8" t="n">
-        <v>252.596335715436</v>
+        <v>34.7868209189557</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.130860024310167</v>
+        <v>3.130860024310173</v>
       </c>
       <c r="AI8" t="n">
         <v>0.9934701919555664</v>
       </c>
       <c r="AJ8" t="n">
-        <v>261.1197552782424</v>
+        <v>43.20927274988051</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.076621197639625</v>
+        <v>1.076621197639628</v>
       </c>
       <c r="AL8" t="n">
         <v>0.9970181286334991</v>
       </c>
       <c r="AM8" t="n">
-        <v>228.9816754929563</v>
+        <v>10.67576306931515</v>
       </c>
       <c r="AN8" t="n">
         <v>14.74588272419382</v>
@@ -2085,7 +2085,7 @@
         <v>0.9994425475597382</v>
       </c>
       <c r="AP8" t="n">
-        <v>193.8172563593438</v>
+        <v>-23.61322362372216</v>
       </c>
       <c r="AQ8" t="n">
         <v>29.45534320587808</v>
@@ -2094,7 +2094,7 @@
         <v>0.8547621071338654</v>
       </c>
       <c r="AS8" t="n">
-        <v>158.6390799664437</v>
+        <v>-59.1306321164395</v>
       </c>
       <c r="AT8" t="n">
         <v>48.68324360948928</v>
@@ -2103,61 +2103,61 @@
         <v>0.9949490427970886</v>
       </c>
       <c r="AV8" t="n">
-        <v>85.86716863618209</v>
+        <v>0.3493826440040237</v>
       </c>
       <c r="AW8" t="n">
-        <v>85.65545277256433</v>
+        <v>-0.734962301051354</v>
       </c>
       <c r="AX8" t="n">
-        <v>87.04884560776014</v>
+        <v>0.9610368850383324</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.3493826440040095</v>
+        <v>-1.029031834703812</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.7349623010513682</v>
+        <v>1.301775587365988</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.9610368850383395</v>
+        <v>-0.4832217033873221</v>
       </c>
       <c r="BB8" t="n">
-        <v>-1.029031834703815</v>
+        <v>1.13383354024684</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.301775587365988</v>
+        <v>-0.4733349414581909</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.4832217033873221</v>
+        <v>1.315847356268698</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.133833540246833</v>
+        <v>-0.3196396726243051</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.473334941458198</v>
+        <v>83.68774917405496</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.315847356268698</v>
+        <v>83.55000382118678</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.3196396726243123</v>
+        <v>87.93601332166492</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.347135866214519</v>
+        <v>2.381593649537752</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-3.016102311575491</v>
+        <v>-2.976221792621033</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.03312108330951347</v>
+        <v>0.0445818613666269</v>
       </c>
       <c r="BL8" t="n">
-        <v>-3.274354455613761</v>
+        <v>-3.239781486286308</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6943984393902021</v>
+        <v>0.73360472130571</v>
       </c>
       <c r="BN8" t="n">
-        <v>-1.986811247833632</v>
+        <v>-1.991393558993975</v>
       </c>
     </row>
     <row r="9">
@@ -2168,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>318.2467665444029</v>
+        <v>99.78277955917602</v>
       </c>
       <c r="D9" t="n">
         <v>15.50919553066822</v>
@@ -2177,34 +2177,34 @@
         <v>0.9956336617469788</v>
       </c>
       <c r="F9" t="n">
-        <v>304.3297351674831</v>
+        <v>85.36016281614914</v>
       </c>
       <c r="G9" t="n">
-        <v>19.54004003646527</v>
+        <v>19.54004003646526</v>
       </c>
       <c r="H9" t="n">
         <v>0.999478667974472</v>
       </c>
       <c r="I9" t="n">
-        <v>278.8495266691167</v>
+        <v>61.24805085202482</v>
       </c>
       <c r="J9" t="n">
-        <v>3.07713772388216</v>
+        <v>3.077137723882148</v>
       </c>
       <c r="K9" t="n">
         <v>0.9987087249755859</v>
       </c>
       <c r="L9" t="n">
-        <v>281.3232929148572</v>
+        <v>62.54266982382916</v>
       </c>
       <c r="M9" t="n">
-        <v>6.865343134453965</v>
+        <v>6.865343134453957</v>
       </c>
       <c r="N9" t="n">
         <v>0.9982081353664398</v>
       </c>
       <c r="O9" t="n">
-        <v>284.4401785667907</v>
+        <v>65.33590682009435</v>
       </c>
       <c r="P9" t="n">
         <v>16.19623062458444</v>
@@ -2213,16 +2213,16 @@
         <v>0.983732670545578</v>
       </c>
       <c r="R9" t="n">
-        <v>291.517078115585</v>
+        <v>73.7125630074359</v>
       </c>
       <c r="S9" t="n">
-        <v>19.12823129207531</v>
+        <v>19.1282312920753</v>
       </c>
       <c r="T9" t="n">
         <v>0.9926234483718872</v>
       </c>
       <c r="U9" t="n">
-        <v>287.6840124738978</v>
+        <v>69.39881304477126</v>
       </c>
       <c r="V9" t="n">
         <v>26.05605023972532</v>
@@ -2231,7 +2231,7 @@
         <v>0.9879996180534363</v>
       </c>
       <c r="X9" t="n">
-        <v>250.9787803000592</v>
+        <v>33.77445505020465</v>
       </c>
       <c r="Y9" t="n">
         <v>25.87550548796958</v>
@@ -2240,7 +2240,7 @@
         <v>0.9681489765644073</v>
       </c>
       <c r="AA9" t="n">
-        <v>247.9477699766768</v>
+        <v>30.85561305918591</v>
       </c>
       <c r="AB9" t="n">
         <v>17.31194841100815</v>
@@ -2249,115 +2249,115 @@
         <v>0.9347332417964935</v>
       </c>
       <c r="AD9" t="n">
-        <v>258.0206850741772</v>
+        <v>40.75597397824552</v>
       </c>
       <c r="AE9" t="n">
-        <v>15.00060710501162</v>
+        <v>15.00060710501164</v>
       </c>
       <c r="AF9" t="n">
         <v>0.9701595604419708</v>
       </c>
       <c r="AG9" t="n">
-        <v>253.0915240023999</v>
+        <v>35.28200920591962</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.528310897502479</v>
+        <v>3.528310897502493</v>
       </c>
       <c r="AI9" t="n">
         <v>0.9958894848823547</v>
       </c>
       <c r="AJ9" t="n">
-        <v>261.0825660380912</v>
+        <v>43.17208350972928</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.7645951940658193</v>
+        <v>0.7645951940658245</v>
       </c>
       <c r="AL9" t="n">
         <v>0.996505469083786</v>
       </c>
       <c r="AM9" t="n">
-        <v>230.5868148803711</v>
+        <v>12.28090245672996</v>
       </c>
       <c r="AN9" t="n">
-        <v>14.56218475991108</v>
+        <v>14.56218475991107</v>
       </c>
       <c r="AO9" t="n">
         <v>0.9996255934238434</v>
       </c>
       <c r="AP9" t="n">
-        <v>195.6327681845807</v>
+        <v>-21.7977117984853</v>
       </c>
       <c r="AQ9" t="n">
-        <v>29.10507689131066</v>
+        <v>29.10507689131067</v>
       </c>
       <c r="AR9" t="n">
         <v>0.9009480476379395</v>
       </c>
       <c r="AS9" t="n">
-        <v>160.3117597864029</v>
+        <v>-57.45795229648023</v>
       </c>
       <c r="AT9" t="n">
-        <v>48.5651746709296</v>
+        <v>48.56517467092961</v>
       </c>
       <c r="AU9" t="n">
         <v>0.9953183531761169</v>
       </c>
       <c r="AV9" t="n">
-        <v>85.8475302941502</v>
+        <v>0.01639914005360765</v>
       </c>
       <c r="AW9" t="n">
-        <v>79.64248140289118</v>
+        <v>0.02792338107493464</v>
       </c>
       <c r="AX9" t="n">
-        <v>83.40722917386699</v>
+        <v>0.2449969027904757</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01639914005362186</v>
+        <v>-0.1413563464550229</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.02792338107494885</v>
+        <v>0.4653200190117985</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2449969027904757</v>
+        <v>-0.2446372458275334</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0.1413563464550265</v>
+        <v>0.5065451277063246</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4653200190117985</v>
+        <v>-0.1384948162322353</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.2446372458275334</v>
+        <v>0.5094599216542335</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.5065451277063318</v>
+        <v>-0.2172150510422703</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.1384948162322281</v>
+        <v>83.81892506381304</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.5094599216542406</v>
+        <v>77.60325166051862</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.2172150510422668</v>
+        <v>84.29345806711596</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0.3357836058594614</v>
+        <v>-0.2963180621539827</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-1.452495683050454</v>
+        <v>-1.482937110939645</v>
       </c>
       <c r="BK9" t="n">
-        <v>-2.439254736092078</v>
+        <v>-2.433726681562643</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.6566829322023491</v>
+        <v>0.656585484775956</v>
       </c>
       <c r="BM9" t="n">
-        <v>-1.36963359559881</v>
+        <v>-1.389048843078029</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.8690944659243112</v>
+        <v>0.8737996762766045</v>
       </c>
     </row>
     <row r="10">
@@ -2368,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>319.2385172590297</v>
+        <v>100.7745302738028</v>
       </c>
       <c r="D10" t="n">
         <v>16.28734507459275</v>
@@ -2377,7 +2377,7 @@
         <v>0.9170281887054443</v>
       </c>
       <c r="F10" t="n">
-        <v>306.5152183492133</v>
+        <v>87.54564599787935</v>
       </c>
       <c r="G10" t="n">
         <v>20.40032731725815</v>
@@ -2386,61 +2386,61 @@
         <v>0.9995072484016418</v>
       </c>
       <c r="I10" t="n">
-        <v>290.9823945228089</v>
+        <v>73.38091870571705</v>
       </c>
       <c r="J10" t="n">
-        <v>4.757641731424542</v>
+        <v>4.757641731424535</v>
       </c>
       <c r="K10" t="n">
         <v>0.8481242060661316</v>
       </c>
       <c r="L10" t="n">
-        <v>293.8311860916463</v>
+        <v>75.05056300061815</v>
       </c>
       <c r="M10" t="n">
-        <v>8.011489218853896</v>
+        <v>8.011489218853891</v>
       </c>
       <c r="N10" t="n">
         <v>0.9869251847267151</v>
       </c>
       <c r="O10" t="n">
-        <v>285.9538484126964</v>
+        <v>66.84957666600005</v>
       </c>
       <c r="P10" t="n">
-        <v>16.53840085293385</v>
+        <v>16.53840085293384</v>
       </c>
       <c r="Q10" t="n">
         <v>0.9777265787124634</v>
       </c>
       <c r="R10" t="n">
-        <v>293.4336844910967</v>
+        <v>75.62916938294757</v>
       </c>
       <c r="S10" t="n">
-        <v>20.1088195151471</v>
+        <v>20.10881951514711</v>
       </c>
       <c r="T10" t="n">
         <v>0.9954724609851837</v>
       </c>
       <c r="U10" t="n">
-        <v>289.6849622117712</v>
+        <v>71.3997627826447</v>
       </c>
       <c r="V10" t="n">
-        <v>26.83832696143618</v>
+        <v>26.83832696143617</v>
       </c>
       <c r="W10" t="n">
         <v>0.9877583384513855</v>
       </c>
       <c r="X10" t="n">
-        <v>251.8576581427392</v>
+        <v>34.65333289288459</v>
       </c>
       <c r="Y10" t="n">
-        <v>24.67521505152925</v>
+        <v>24.67521505152926</v>
       </c>
       <c r="Z10" t="n">
         <v>0.9582006335258484</v>
       </c>
       <c r="AA10" t="n">
-        <v>248.7501834301239</v>
+        <v>31.65802651263297</v>
       </c>
       <c r="AB10" t="n">
         <v>16.25941662078208</v>
@@ -2449,7 +2449,7 @@
         <v>0.9784192144870758</v>
       </c>
       <c r="AD10" t="n">
-        <v>258.6692870931423</v>
+        <v>41.40457599721057</v>
       </c>
       <c r="AE10" t="n">
         <v>13.87882638484874</v>
@@ -2458,43 +2458,43 @@
         <v>0.9645244181156158</v>
       </c>
       <c r="AG10" t="n">
-        <v>253.0212869035437</v>
+        <v>35.21177210706345</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.907399928316138</v>
+        <v>2.907399928316157</v>
       </c>
       <c r="AI10" t="n">
         <v>0.9967203438282013</v>
       </c>
       <c r="AJ10" t="n">
-        <v>261.1570703222396</v>
+        <v>43.24658779387778</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.3810476749501248</v>
+        <v>0.381047674950133</v>
       </c>
       <c r="AL10" t="n">
         <v>0.9978673756122589</v>
       </c>
       <c r="AM10" t="n">
-        <v>231.0847667937583</v>
+        <v>12.77885437011719</v>
       </c>
       <c r="AN10" t="n">
-        <v>13.71540313071392</v>
+        <v>13.71540313071393</v>
       </c>
       <c r="AO10" t="n">
         <v>0.9986975193023682</v>
       </c>
       <c r="AP10" t="n">
-        <v>196.5577389331574</v>
+        <v>-20.87274104990858</v>
       </c>
       <c r="AQ10" t="n">
-        <v>27.94880968459108</v>
+        <v>27.94880968459109</v>
       </c>
       <c r="AR10" t="n">
         <v>0.9468184411525726</v>
       </c>
       <c r="AS10" t="n">
-        <v>160.7955770289644</v>
+        <v>-56.97413505391872</v>
       </c>
       <c r="AT10" t="n">
         <v>46.94547450288813</v>
@@ -2503,61 +2503,61 @@
         <v>0.9963061809539795</v>
       </c>
       <c r="AV10" t="n">
-        <v>80.01790921991652</v>
+        <v>0.0545714763884888</v>
       </c>
       <c r="AW10" t="n">
-        <v>76.25624176202741</v>
+        <v>0.06795030959109738</v>
       </c>
       <c r="AX10" t="n">
-        <v>83.2419906036711</v>
+        <v>-0.1299442128932213</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.05457147638847459</v>
+        <v>0.02308957120205335</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.06795030959108317</v>
+        <v>0.1614408290132587</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.1299442128932355</v>
+        <v>-0.1197003303690138</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0230895712020569</v>
+        <v>0.1617046112709914</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.1614408290132587</v>
+        <v>-0.1464945204714496</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.1197003303690138</v>
+        <v>0.3502795036802908</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.1617046112709843</v>
+        <v>-0.1614986582005287</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.1464945204714567</v>
+        <v>78.01835250981254</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.3502795036802837</v>
+        <v>74.28284143895428</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.1614986582005287</v>
+        <v>84.14610151767343</v>
       </c>
       <c r="BI10" t="n">
-        <v>-2.545205647848839</v>
+        <v>-2.536777332686651</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.318678108178574</v>
+        <v>1.312575124596458</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0.8385597261191329</v>
+        <v>-0.8033855207497034</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.2976448409808228</v>
+        <v>0.2785627824975681</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.6512253799678476</v>
+        <v>-0.641385440840029</v>
       </c>
       <c r="BN10" t="n">
-        <v>-0.2811413822243942</v>
+        <v>-0.2909609428973514</v>
       </c>
     </row>
     <row r="11">
@@ -2568,16 +2568,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>319.844918143242</v>
+        <v>101.3809311580151</v>
       </c>
       <c r="D11" t="n">
-        <v>15.55397358346492</v>
+        <v>15.55397358346493</v>
       </c>
       <c r="E11" t="n">
         <v>0.6346573531627655</v>
       </c>
       <c r="F11" t="n">
-        <v>307.5024873652357</v>
+        <v>88.53291501390174</v>
       </c>
       <c r="G11" t="n">
         <v>20.03302066884142</v>
@@ -2586,16 +2586,16 @@
         <v>0.9997338652610779</v>
       </c>
       <c r="I11" t="n">
-        <v>301.8907678888199</v>
+        <v>84.289292071728</v>
       </c>
       <c r="J11" t="n">
-        <v>6.088565258269597</v>
+        <v>6.088565258269615</v>
       </c>
       <c r="K11" t="n">
         <v>0.9930191338062286</v>
       </c>
       <c r="L11" t="n">
-        <v>299.3656909212153</v>
+        <v>80.5850678301872</v>
       </c>
       <c r="M11" t="n">
         <v>8.102132918986868</v>
@@ -2604,16 +2604,16 @@
         <v>0.9932544827461243</v>
       </c>
       <c r="O11" t="n">
-        <v>289.3964564546626</v>
+        <v>70.29218470796627</v>
       </c>
       <c r="P11" t="n">
-        <v>14.54578156166889</v>
+        <v>14.54578156166888</v>
       </c>
       <c r="Q11" t="n">
         <v>0.9739580452442169</v>
       </c>
       <c r="R11" t="n">
-        <v>295.6117711168655</v>
+        <v>77.80725600871634</v>
       </c>
       <c r="S11" t="n">
         <v>19.31800842285156</v>
@@ -2622,7 +2622,7 @@
         <v>0.993291050195694</v>
       </c>
       <c r="U11" t="n">
-        <v>290.9026886554475</v>
+        <v>72.61748922632094</v>
       </c>
       <c r="V11" t="n">
         <v>26.11548241148604</v>
@@ -2631,7 +2631,7 @@
         <v>0.9876150488853455</v>
       </c>
       <c r="X11" t="n">
-        <v>252.090541352617</v>
+        <v>34.88621610276242</v>
       </c>
       <c r="Y11" t="n">
         <v>23.63709794714096</v>
@@ -2640,7 +2640,7 @@
         <v>0.9762316644191742</v>
       </c>
       <c r="AA11" t="n">
-        <v>248.9666188016851</v>
+        <v>31.87446188419423</v>
       </c>
       <c r="AB11" t="n">
         <v>15.18696724100316</v>
@@ -2649,7 +2649,7 @@
         <v>0.9858298599720001</v>
       </c>
       <c r="AD11" t="n">
-        <v>258.8390877906313</v>
+        <v>41.57437669469957</v>
       </c>
       <c r="AE11" t="n">
         <v>13.04318042511636</v>
@@ -2658,16 +2658,16 @@
         <v>0.966762900352478</v>
       </c>
       <c r="AG11" t="n">
-        <v>253.0434080894958</v>
+        <v>35.2338932930155</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.226192393201472</v>
+        <v>2.226192393201463</v>
       </c>
       <c r="AI11" t="n">
         <v>0.994694709777832</v>
       </c>
       <c r="AJ11" t="n">
-        <v>261.5033758447526</v>
+        <v>43.59289331639067</v>
       </c>
       <c r="AK11" t="n">
         <v>-0.466156005859375</v>
@@ -2676,25 +2676,25 @@
         <v>0.9978399872779846</v>
       </c>
       <c r="AM11" t="n">
-        <v>231.9059169038813</v>
+        <v>13.60000448024019</v>
       </c>
       <c r="AN11" t="n">
-        <v>12.2843235097033</v>
+        <v>12.28432350970329</v>
       </c>
       <c r="AO11" t="n">
         <v>0.9992930889129639</v>
       </c>
       <c r="AP11" t="n">
-        <v>196.6846506646339</v>
+        <v>-20.7458293184321</v>
       </c>
       <c r="AQ11" t="n">
-        <v>25.98620475606715</v>
+        <v>25.98620475606716</v>
       </c>
       <c r="AR11" t="n">
         <v>0.9268379807472229</v>
       </c>
       <c r="AS11" t="n">
-        <v>160.9967576696517</v>
+        <v>-56.77295441323139</v>
       </c>
       <c r="AT11" t="n">
         <v>44.43270500670089</v>
@@ -2703,72 +2703,72 @@
         <v>0.9971371591091156</v>
       </c>
       <c r="AV11" t="n">
-        <v>79.46300057839713</v>
+        <v>0.226000522045382</v>
       </c>
       <c r="AW11" t="n">
-        <v>74.06058148508694</v>
+        <v>-0.05540188322676443</v>
       </c>
       <c r="AX11" t="n">
-        <v>81.95218650457763</v>
+        <v>-0.02426796771110418</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.226000522045382</v>
+        <v>0.001157598292572004</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.05540188322675021</v>
+        <v>0.1544008863733097</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0.02426796771109707</v>
+        <v>0.09720477652041382</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.001157598292572004</v>
+        <v>0.1775214012632986</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.1544008863733239</v>
+        <v>0.07772141314567449</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.09720477652042092</v>
+        <v>0.1538367981606328</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.1775214012632986</v>
+        <v>0.241372940388132</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.07772141314567804</v>
+        <v>77.46808045419789</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.1538367981606328</v>
+        <v>72.07668234738023</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.241372940388132</v>
+        <v>82.83490119664148</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0.753824504493938</v>
+        <v>-0.7285706363528881</v>
       </c>
       <c r="BJ11" t="n">
-        <v>-0.6460284727248204</v>
+        <v>-0.6268954863903069</v>
       </c>
       <c r="BK11" t="n">
-        <v>-1.579036141572708</v>
+        <v>-1.561283840834243</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.2150658766267703</v>
+        <v>0.2439748468826064</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.7102443532927936</v>
+        <v>-0.7250074075534663</v>
       </c>
       <c r="BN11" t="n">
-        <v>-0.5644104426267837</v>
+        <v>-0.5632759497776512</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6.845</v>
+        <v>6.845000000000001</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>319.5510957786377</v>
+        <v>101.0871087934108</v>
       </c>
       <c r="D12" t="n">
         <v>12.89043020694814</v>
@@ -2777,52 +2777,52 @@
         <v>0.5624549686908722</v>
       </c>
       <c r="F12" t="n">
-        <v>308.9899438492796</v>
+        <v>90.0203714979456</v>
       </c>
       <c r="G12" t="n">
-        <v>18.79907973269198</v>
+        <v>18.79907973269199</v>
       </c>
       <c r="H12" t="n">
         <v>0.9994161128997803</v>
       </c>
       <c r="I12" t="n">
-        <v>306.2310305047542</v>
+        <v>88.62955468766233</v>
       </c>
       <c r="J12" t="n">
-        <v>6.153204085979041</v>
+        <v>6.153204085979056</v>
       </c>
       <c r="K12" t="n">
         <v>0.9947877824306488</v>
       </c>
       <c r="L12" t="n">
-        <v>303.1455932779515</v>
+        <v>84.36497018692341</v>
       </c>
       <c r="M12" t="n">
-        <v>7.52595942071143</v>
+        <v>7.525959420711437</v>
       </c>
       <c r="N12" t="n">
         <v>0.9970605969429016</v>
       </c>
       <c r="O12" t="n">
-        <v>292.0716021923309</v>
+        <v>72.96733044563453</v>
       </c>
       <c r="P12" t="n">
-        <v>13.43140297747672</v>
+        <v>13.43140297747673</v>
       </c>
       <c r="Q12" t="n">
         <v>0.9784769713878632</v>
       </c>
       <c r="R12" t="n">
-        <v>297.6283377789437</v>
+        <v>79.82382267079453</v>
       </c>
       <c r="S12" t="n">
-        <v>18.39230314214178</v>
+        <v>18.39230314214179</v>
       </c>
       <c r="T12" t="n">
         <v>0.9946500658988953</v>
       </c>
       <c r="U12" t="n">
-        <v>293.0585323496068</v>
+        <v>74.7733329204803</v>
       </c>
       <c r="V12" t="n">
         <v>25.42912503506275</v>
@@ -2831,7 +2831,7 @@
         <v>0.980243593454361</v>
       </c>
       <c r="X12" t="n">
-        <v>253.2889163240473</v>
+        <v>36.08459107419277</v>
       </c>
       <c r="Y12" t="n">
         <v>23.45689814141456</v>
@@ -2840,25 +2840,25 @@
         <v>0.9690394997596741</v>
       </c>
       <c r="AA12" t="n">
-        <v>249.493939825829</v>
+        <v>32.40178290833819</v>
       </c>
       <c r="AB12" t="n">
-        <v>15.1650530226687</v>
+        <v>15.16505302266872</v>
       </c>
       <c r="AC12" t="n">
         <v>0.9935588836669922</v>
       </c>
       <c r="AD12" t="n">
-        <v>259.397707594202</v>
+        <v>42.13299649827022</v>
       </c>
       <c r="AE12" t="n">
-        <v>12.88324721316073</v>
+        <v>12.88324721316074</v>
       </c>
       <c r="AF12" t="n">
         <v>0.9697324335575104</v>
       </c>
       <c r="AG12" t="n">
-        <v>253.0701596686181</v>
+        <v>35.26064487213783</v>
       </c>
       <c r="AH12" t="n">
         <v>2.036188003864694</v>
@@ -2867,34 +2867,34 @@
         <v>0.9941236674785614</v>
       </c>
       <c r="AJ12" t="n">
-        <v>261.6280738343584</v>
+        <v>43.71759130599651</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.5079959301238404</v>
+        <v>-0.5079959301238365</v>
       </c>
       <c r="AL12" t="n">
         <v>0.9977763891220093</v>
       </c>
       <c r="AM12" t="n">
-        <v>233.0243942585397</v>
+        <v>14.7184818348986</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.26392705389793</v>
+        <v>12.26392705389794</v>
       </c>
       <c r="AO12" t="n">
         <v>0.9996479451656342</v>
       </c>
       <c r="AP12" t="n">
-        <v>197.3862871210626</v>
+        <v>-20.04419286200341</v>
       </c>
       <c r="AQ12" t="n">
-        <v>24.70871539826088</v>
+        <v>24.70871539826089</v>
       </c>
       <c r="AR12" t="n">
         <v>0.9175179302692413</v>
       </c>
       <c r="AS12" t="n">
-        <v>161.7745825584898</v>
+        <v>-55.99512952439329</v>
       </c>
       <c r="AT12" t="n">
         <v>42.24735422337309</v>
@@ -2903,61 +2903,61 @@
         <v>0.9947538375854492</v>
       </c>
       <c r="AV12" t="n">
-        <v>76.32397804597844</v>
+        <v>-0.05416667207759929</v>
       </c>
       <c r="AW12" t="n">
-        <v>72.72518471465357</v>
+        <v>-0.05936318255485418</v>
       </c>
       <c r="AX12" t="n">
-        <v>78.40474063497702</v>
+        <v>0.1375482437458402</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.05416667207758508</v>
+        <v>0.04846643894276781</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.05936318255486128</v>
+        <v>0.353405323434373</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.1375482437458473</v>
+        <v>0.06117871467104408</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.04846643894277136</v>
+        <v>0.2531396581771546</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.353405323434373</v>
+        <v>0.03757781170783758</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.06117871467103697</v>
+        <v>0.7076588082820905</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.2531396581771546</v>
+        <v>-0.04704759476032194</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.03757781170783758</v>
+        <v>74.41022645302199</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.7076588082820834</v>
+        <v>70.84642264333658</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.0470475947603255</v>
+        <v>79.27059707649894</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.7409935772324445</v>
+        <v>-0.703975780532744</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-0.07218304988355229</v>
+        <v>-0.07322091111016071</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0.2858520258250365</v>
+        <v>-0.2462176891398826</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.2702893461898075</v>
+        <v>0.2726667750648062</v>
       </c>
       <c r="BM12" t="n">
-        <v>-2.174703338084576</v>
+        <v>-2.184130883482766</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.9075428166049804</v>
+        <v>0.9219229237535114</v>
       </c>
     </row>
     <row r="13">
@@ -2968,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>320.2977028932977</v>
+        <v>101.8337159080708</v>
       </c>
       <c r="D13" t="n">
         <v>11.54108250394781</v>
@@ -2977,61 +2977,61 @@
         <v>0.3866619467735291</v>
       </c>
       <c r="F13" t="n">
-        <v>310.3578187049704</v>
+        <v>91.38824635363639</v>
       </c>
       <c r="G13" t="n">
-        <v>17.47839907382398</v>
+        <v>17.47839907382397</v>
       </c>
       <c r="H13" t="n">
         <v>0.9990964233875275</v>
       </c>
       <c r="I13" t="n">
-        <v>308.1125731163836</v>
+        <v>90.51109729929172</v>
       </c>
       <c r="J13" t="n">
-        <v>4.848942858107563</v>
+        <v>4.848942858107547</v>
       </c>
       <c r="K13" t="n">
         <v>0.9927547872066498</v>
       </c>
       <c r="L13" t="n">
-        <v>304.7039143582608</v>
+        <v>85.92329126723268</v>
       </c>
       <c r="M13" t="n">
-        <v>6.155955537836618</v>
+        <v>6.155955537836602</v>
       </c>
       <c r="N13" t="n">
         <v>0.9827735722064972</v>
       </c>
       <c r="O13" t="n">
-        <v>293.8964945204715</v>
+        <v>74.79222277377514</v>
       </c>
       <c r="P13" t="n">
-        <v>12.95000441530919</v>
+        <v>12.95000441530918</v>
       </c>
       <c r="Q13" t="n">
         <v>0.9821538329124451</v>
       </c>
       <c r="R13" t="n">
-        <v>299.7064397690144</v>
+        <v>81.90192466086532</v>
       </c>
       <c r="S13" t="n">
-        <v>17.69832042937584</v>
+        <v>17.69832042937583</v>
       </c>
       <c r="T13" t="n">
         <v>0.9928506910800934</v>
       </c>
       <c r="U13" t="n">
-        <v>295.3197874921434</v>
+        <v>77.03458806301683</v>
       </c>
       <c r="V13" t="n">
-        <v>25.02955984562003</v>
+        <v>25.02955984562001</v>
       </c>
       <c r="W13" t="n">
         <v>0.9803042113780975</v>
       </c>
       <c r="X13" t="n">
-        <v>254.2991009164364</v>
+        <v>37.09477566658184</v>
       </c>
       <c r="Y13" t="n">
         <v>22.93585919319315</v>
@@ -3040,7 +3040,7 @@
         <v>0.959033340215683</v>
       </c>
       <c r="AA13" t="n">
-        <v>250.1715720968044</v>
+        <v>33.0794151793135</v>
       </c>
       <c r="AB13" t="n">
         <v>15.00349653528092</v>
@@ -3049,7 +3049,7 @@
         <v>0.9900617301464081</v>
       </c>
       <c r="AD13" t="n">
-        <v>260.2010422564568</v>
+        <v>42.93633116052504</v>
       </c>
       <c r="AE13" t="n">
         <v>12.13998185827377</v>
@@ -3058,34 +3058,34 @@
         <v>0.976091206073761</v>
       </c>
       <c r="AG13" t="n">
-        <v>253.2907770035115</v>
+        <v>35.48126220703124</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.694034008269611</v>
+        <v>1.694034008269615</v>
       </c>
       <c r="AI13" t="n">
         <v>0.9933938384056091</v>
       </c>
       <c r="AJ13" t="n">
-        <v>261.5153190937448</v>
+        <v>43.60483656538293</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.7298895653258057</v>
+        <v>-0.729889565325798</v>
       </c>
       <c r="AL13" t="n">
         <v>0.9978114068508148</v>
       </c>
       <c r="AM13" t="n">
-        <v>234.077388682264</v>
+        <v>15.77147625862284</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.12719044786819</v>
+        <v>12.12719044786818</v>
       </c>
       <c r="AO13" t="n">
         <v>0.9997440278530121</v>
       </c>
       <c r="AP13" t="n">
-        <v>198.5893249511719</v>
+        <v>-18.84115503189413</v>
       </c>
       <c r="AQ13" t="n">
         <v>23.43234610050283</v>
@@ -3094,70 +3094,70 @@
         <v>0.9492345154285431</v>
       </c>
       <c r="AS13" t="n">
-        <v>162.8531679194024</v>
+        <v>-54.91654416348072</v>
       </c>
       <c r="AT13" t="n">
-        <v>40.28646590861869</v>
+        <v>40.28646590861868</v>
       </c>
       <c r="AU13" t="n">
         <v>0.9935709834098816</v>
       </c>
       <c r="AV13" t="n">
-        <v>72.89622331402555</v>
+        <v>-0.03535088072432302</v>
       </c>
       <c r="AW13" t="n">
-        <v>72.47094532897941</v>
+        <v>0.03310315152432253</v>
       </c>
       <c r="AX13" t="n">
-        <v>78.48746603179633</v>
+        <v>0.1108118828306814</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.03535088072430881</v>
+        <v>0.06774993652993544</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.03310315152432253</v>
+        <v>0.2965440141393856</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.1108118828306814</v>
+        <v>-0.01954474347702728</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.06774993652992833</v>
+        <v>0.4872301791576561</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.2965440141393856</v>
+        <v>0.02767025156223824</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0.01954474347702728</v>
+        <v>0.4761868334831121</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.4872301791576561</v>
+        <v>-0.01073796698388563</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.02767025156224179</v>
+        <v>71.05948880740546</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.4761868334831121</v>
+        <v>70.70683003955216</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.01073796698387852</v>
+        <v>79.39398465137045</v>
       </c>
       <c r="BI13" t="n">
-        <v>-2.713972332160104</v>
+        <v>-2.714269493319488</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.05167096480444933</v>
+        <v>0.03565566176883195</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.391681682230487</v>
+        <v>1.449468020376365</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.2176911591280284</v>
+        <v>0.2026579066622425</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.649219458863218</v>
+        <v>2.707961186672915</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.2671646863361055</v>
+        <v>0.2663338903422865</v>
       </c>
     </row>
     <row r="14">
@@ -3168,16 +3168,16 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>320.2721853522544</v>
+        <v>101.8081983670275</v>
       </c>
       <c r="D14" t="n">
-        <v>8.800847479637625</v>
+        <v>8.800847479637634</v>
       </c>
       <c r="E14" t="n">
         <v>0.09001572243869305</v>
       </c>
       <c r="F14" t="n">
-        <v>311.7964151057791</v>
+        <v>92.82684275444518</v>
       </c>
       <c r="G14" t="n">
         <v>16.59569435931267</v>
@@ -3186,25 +3186,25 @@
         <v>0.9997400641441345</v>
       </c>
       <c r="I14" t="n">
-        <v>308.4794622786502</v>
+        <v>90.87798646155824</v>
       </c>
       <c r="J14" t="n">
-        <v>3.895430869244507</v>
+        <v>3.895430869244515</v>
       </c>
       <c r="K14" t="n">
         <v>0.9983626008033752</v>
       </c>
       <c r="L14" t="n">
-        <v>305.0724455650816</v>
+        <v>86.29182247405356</v>
       </c>
       <c r="M14" t="n">
-        <v>5.273518663771597</v>
+        <v>5.273518663771609</v>
       </c>
       <c r="N14" t="n">
         <v>0.9706786870956421</v>
       </c>
       <c r="O14" t="n">
-        <v>295.2345716192367</v>
+        <v>76.13029987254041</v>
       </c>
       <c r="P14" t="n">
         <v>12.91385407143451</v>
@@ -3213,25 +3213,25 @@
         <v>0.9750039875507355</v>
       </c>
       <c r="R14" t="n">
-        <v>301.2238928612243</v>
+        <v>83.41937775307511</v>
       </c>
       <c r="S14" t="n">
-        <v>17.07091635846076</v>
+        <v>17.07091635846077</v>
       </c>
       <c r="T14" t="n">
         <v>0.992463231086731</v>
       </c>
       <c r="U14" t="n">
-        <v>297.3184210188846</v>
+        <v>79.03322158975806</v>
       </c>
       <c r="V14" t="n">
-        <v>24.45132478754572</v>
+        <v>24.45132478754571</v>
       </c>
       <c r="W14" t="n">
         <v>0.9870566129684448</v>
       </c>
       <c r="X14" t="n">
-        <v>255.2663336408899</v>
+        <v>38.06200839103536</v>
       </c>
       <c r="Y14" t="n">
         <v>22.96379576338099</v>
@@ -3240,16 +3240,16 @@
         <v>0.9757921695709229</v>
       </c>
       <c r="AA14" t="n">
-        <v>250.9598853740286</v>
+        <v>33.86772845653776</v>
       </c>
       <c r="AB14" t="n">
-        <v>15.21099171739945</v>
+        <v>15.21099171739944</v>
       </c>
       <c r="AC14" t="n">
         <v>0.9880344867706299</v>
       </c>
       <c r="AD14" t="n">
-        <v>260.9261979448035</v>
+        <v>43.66148684887176</v>
       </c>
       <c r="AE14" t="n">
         <v>11.84359611348903</v>
@@ -3258,106 +3258,106 @@
         <v>0.9843989610671997</v>
       </c>
       <c r="AG14" t="n">
-        <v>253.7823940845246</v>
+        <v>35.97287928804438</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.87049216412484</v>
+        <v>1.870492164124834</v>
       </c>
       <c r="AI14" t="n">
         <v>0.9957489967346191</v>
       </c>
       <c r="AJ14" t="n">
-        <v>261.5349769592285</v>
+        <v>43.62449443086663</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.2483854902551457</v>
+        <v>-0.2483854902551529</v>
       </c>
       <c r="AL14" t="n">
         <v>0.9976234138011932</v>
       </c>
       <c r="AM14" t="n">
-        <v>235.6123376399913</v>
+        <v>17.30642521635015</v>
       </c>
       <c r="AN14" t="n">
-        <v>12.69920836103725</v>
+        <v>12.69920836103724</v>
       </c>
       <c r="AO14" t="n">
         <v>0.9992619454860687</v>
       </c>
       <c r="AP14" t="n">
-        <v>200.1429375181807</v>
+        <v>-17.28754246488532</v>
       </c>
       <c r="AQ14" t="n">
-        <v>23.22772411589928</v>
+        <v>23.22772411589927</v>
       </c>
       <c r="AR14" t="n">
         <v>0.9494307935237885</v>
       </c>
       <c r="AS14" t="n">
-        <v>163.7677212978931</v>
+        <v>-54.00199078499004</v>
       </c>
       <c r="AT14" t="n">
-        <v>38.69444664488449</v>
+        <v>38.69444664488448</v>
       </c>
       <c r="AU14" t="n">
         <v>0.9897622168064117</v>
       </c>
       <c r="AV14" t="n">
-        <v>69.67515244129046</v>
+        <v>0.1289631458039082</v>
       </c>
       <c r="AW14" t="n">
-        <v>73.08747057981736</v>
+        <v>0.08846546741242634</v>
       </c>
       <c r="AX14" t="n">
-        <v>79.63885017396007</v>
+        <v>0.2566743404307346</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.1289631458038798</v>
+        <v>-0.03065200562173231</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.08846546741241923</v>
+        <v>0.5954468503911556</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.2566743404307203</v>
+        <v>0.1326287046391883</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0.03065200562172876</v>
+        <v>0.3607658629721797</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.5954468503911414</v>
+        <v>0.08583119575014209</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.1326287046391812</v>
+        <v>0.358833150660729</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.3607658629721868</v>
+        <v>-0.08859482217341608</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.08583119575013498</v>
+        <v>67.85137380886425</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.3588331506607361</v>
+        <v>71.37786906241672</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.08859482217342318</v>
+        <v>80.5827077876111</v>
       </c>
       <c r="BI14" t="n">
-        <v>-1.378140322561389</v>
+        <v>-1.312248305463591</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.2166207341138033</v>
+        <v>0.2575882303927965</v>
       </c>
       <c r="BK14" t="n">
-        <v>-1.970498473016448</v>
+        <v>-1.923268542404703</v>
       </c>
       <c r="BL14" t="n">
-        <v>-1.088968854148783</v>
+        <v>-1.063689427113044</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.6703446647619948</v>
+        <v>-0.6834073397537637</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.5854172251881611</v>
+        <v>0.5789762304473776</v>
       </c>
     </row>
     <row r="15">
@@ -3368,70 +3368,70 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>305.9890462997112</v>
+        <v>87.52505931448428</v>
       </c>
       <c r="D15" t="n">
-        <v>4.846718970765451</v>
+        <v>4.846718970765459</v>
       </c>
       <c r="E15" t="n">
         <v>0.01314319437369704</v>
       </c>
       <c r="F15" t="n">
-        <v>314.0310206311815</v>
+        <v>95.0614482798475</v>
       </c>
       <c r="G15" t="n">
-        <v>16.55413850824883</v>
+        <v>16.55413850824884</v>
       </c>
       <c r="H15" t="n">
         <v>0.9989054799079895</v>
       </c>
       <c r="I15" t="n">
-        <v>308.8347394415673</v>
+        <v>91.23326362447537</v>
       </c>
       <c r="J15" t="n">
-        <v>4.044293342752653</v>
+        <v>4.04429334275266</v>
       </c>
       <c r="K15" t="n">
         <v>0.9975409507751465</v>
       </c>
       <c r="L15" t="n">
-        <v>305.443475601521</v>
+        <v>86.66285251049285</v>
       </c>
       <c r="M15" t="n">
-        <v>5.436292607733535</v>
+        <v>5.436292607733543</v>
       </c>
       <c r="N15" t="n">
         <v>0.9763016998767853</v>
       </c>
       <c r="O15" t="n">
-        <v>296.3522951653663</v>
+        <v>77.24802341866999</v>
       </c>
       <c r="P15" t="n">
-        <v>13.54718309767702</v>
+        <v>13.54718309767703</v>
       </c>
       <c r="Q15" t="n">
         <v>0.9655660092830658</v>
       </c>
       <c r="R15" t="n">
-        <v>303.1517825228103</v>
+        <v>85.34726741466116</v>
       </c>
       <c r="S15" t="n">
-        <v>17.56445702086103</v>
+        <v>17.56445702086104</v>
       </c>
       <c r="T15" t="n">
         <v>0.9876245856285095</v>
       </c>
       <c r="U15" t="n">
-        <v>299.0190850927475</v>
+        <v>80.73388566362098</v>
       </c>
       <c r="V15" t="n">
-        <v>24.6096022585605</v>
+        <v>24.60960225856051</v>
       </c>
       <c r="W15" t="n">
         <v>0.9813322722911835</v>
       </c>
       <c r="X15" t="n">
-        <v>255.8791870766498</v>
+        <v>38.67486182679522</v>
       </c>
       <c r="Y15" t="n">
         <v>22.91437514284824</v>
@@ -3440,7 +3440,7 @@
         <v>0.9832954704761505</v>
       </c>
       <c r="AA15" t="n">
-        <v>252.0915234342534</v>
+        <v>34.99936651676259</v>
       </c>
       <c r="AB15" t="n">
         <v>14.88377185578042</v>
@@ -3449,34 +3449,34 @@
         <v>0.9858841300010681</v>
       </c>
       <c r="AD15" t="n">
-        <v>262.1818684517069</v>
+        <v>44.91715735577523</v>
       </c>
       <c r="AE15" t="n">
-        <v>11.52929752431018</v>
+        <v>11.52929752431017</v>
       </c>
       <c r="AF15" t="n">
         <v>0.9824780225753784</v>
       </c>
       <c r="AG15" t="n">
-        <v>254.1514031430509</v>
+        <v>36.3418883465706</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.627414784532903</v>
+        <v>1.627414784532912</v>
       </c>
       <c r="AI15" t="n">
         <v>0.9959445595741272</v>
       </c>
       <c r="AJ15" t="n">
-        <v>261.9084966943619</v>
+        <v>43.99801416600005</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.6448948636968055</v>
+        <v>-0.6448948636968086</v>
       </c>
       <c r="AL15" t="n">
         <v>0.9979354739189148</v>
       </c>
       <c r="AM15" t="n">
-        <v>237.6516098671771</v>
+        <v>19.34569744353598</v>
       </c>
       <c r="AN15" t="n">
         <v>12.7762571294257</v>
@@ -3485,16 +3485,16 @@
         <v>0.9994629621505737</v>
       </c>
       <c r="AP15" t="n">
-        <v>201.8253001760929</v>
+        <v>-15.60517980697307</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22.04555754965925</v>
+        <v>22.04555754965924</v>
       </c>
       <c r="AR15" t="n">
         <v>0.9581031203269958</v>
       </c>
       <c r="AS15" t="n">
-        <v>165.0401663272939</v>
+        <v>-52.72954575558927</v>
       </c>
       <c r="AT15" t="n">
         <v>36.98469933043135</v>
@@ -3503,61 +3503,61 @@
         <v>0.9947659075260162</v>
       </c>
       <c r="AV15" t="n">
-        <v>67.32056450501059</v>
+        <v>0.04698367829018935</v>
       </c>
       <c r="AW15" t="n">
-        <v>69.34812041406019</v>
+        <v>-0.08796783203774794</v>
       </c>
       <c r="AX15" t="n">
-        <v>83.13190321687645</v>
+        <v>0.2438869882137169</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.04698367829018935</v>
+        <v>0.02098032768736857</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0.08796783203774083</v>
+        <v>0.5842330607962083</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.2438869882137311</v>
+        <v>-0.09967672063949351</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.02098032768736857</v>
+        <v>0.6308738221513437</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.5842330607962083</v>
+        <v>-0.03350795583522626</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.0996767206394864</v>
+        <v>0.2548633737767005</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.6308738221513437</v>
+        <v>0.0242192694481318</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.03350795583521915</v>
+        <v>65.67361173189423</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.2548633737766934</v>
+        <v>67.79415037682909</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.02421926944813535</v>
+        <v>84.08733584564125</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0.1792255276573904</v>
+        <v>-0.09884394647908934</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6503728416727572</v>
+        <v>0.6331686286168736</v>
       </c>
       <c r="BK15" t="n">
-        <v>-1.724865494991221</v>
+        <v>-1.666804590132696</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.1631229692098106</v>
+        <v>0.1395104241528067</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.55454936590117</v>
+        <v>2.560744517448782</v>
       </c>
       <c r="BN15" t="n">
-        <v>-0.4153715248869201</v>
+        <v>-0.419851212169231</v>
       </c>
     </row>
     <row r="16">
@@ -3568,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>239.3891476570292</v>
+        <v>20.92516067180229</v>
       </c>
       <c r="D16" t="n">
         <v>22.53004033514794</v>
@@ -3577,7 +3577,7 @@
         <v>0.05064057745039463</v>
       </c>
       <c r="F16" t="n">
-        <v>315.6415142911546</v>
+        <v>96.67194193982064</v>
       </c>
       <c r="G16" t="n">
         <v>16.92406674648853</v>
@@ -3586,25 +3586,25 @@
         <v>0.9977730214595795</v>
       </c>
       <c r="I16" t="n">
-        <v>311.1831971939574</v>
+        <v>93.58172137686549</v>
       </c>
       <c r="J16" t="n">
-        <v>6.438348648395959</v>
+        <v>6.438348648395944</v>
       </c>
       <c r="K16" t="n">
         <v>0.9916700124740601</v>
       </c>
       <c r="L16" t="n">
-        <v>308.6445037354814</v>
+        <v>89.86388064445333</v>
       </c>
       <c r="M16" t="n">
-        <v>8.168078483419222</v>
+        <v>8.168078483419215</v>
       </c>
       <c r="N16" t="n">
         <v>0.9858044683933258</v>
       </c>
       <c r="O16" t="n">
-        <v>299.1620976874169</v>
+        <v>80.05782594072056</v>
       </c>
       <c r="P16" t="n">
         <v>14.41821646183095</v>
@@ -3613,16 +3613,16 @@
         <v>0.9570659995079041</v>
       </c>
       <c r="R16" t="n">
-        <v>305.0218399534834</v>
+        <v>87.2173248453343</v>
       </c>
       <c r="S16" t="n">
-        <v>18.22776794433595</v>
+        <v>18.22776794433594</v>
       </c>
       <c r="T16" t="n">
         <v>0.9897854030132294</v>
       </c>
       <c r="U16" t="n">
-        <v>301.7044290583185</v>
+        <v>83.41922962919193</v>
       </c>
       <c r="V16" t="n">
         <v>25.03925079995014</v>
@@ -3631,52 +3631,52 @@
         <v>0.9811103641986847</v>
       </c>
       <c r="X16" t="n">
-        <v>256.5889175902022</v>
+        <v>39.38459234034761</v>
       </c>
       <c r="Y16" t="n">
-        <v>22.24820725461269</v>
+        <v>22.2482072546127</v>
       </c>
       <c r="Z16" t="n">
         <v>0.9899413883686066</v>
       </c>
       <c r="AA16" t="n">
-        <v>253.0891296711374</v>
+        <v>35.99697275364652</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.89099283421292</v>
+        <v>13.89099283421293</v>
       </c>
       <c r="AC16" t="n">
         <v>0.9896542727947235</v>
       </c>
       <c r="AD16" t="n">
-        <v>263.0388320760525</v>
+        <v>45.77412098012073</v>
       </c>
       <c r="AE16" t="n">
-        <v>10.72147450548536</v>
+        <v>10.72147450548537</v>
       </c>
       <c r="AF16" t="n">
         <v>0.9786993265151978</v>
       </c>
       <c r="AG16" t="n">
-        <v>254.6043335123265</v>
+        <v>36.79481871584629</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.159513757583937</v>
+        <v>1.159513757583943</v>
       </c>
       <c r="AI16" t="n">
         <v>0.9969850182533264</v>
       </c>
       <c r="AJ16" t="n">
-        <v>261.9301451013444</v>
+        <v>44.01966257298247</v>
       </c>
       <c r="AK16" t="n">
-        <v>-1.35945259256566</v>
+        <v>-1.359452592565658</v>
       </c>
       <c r="AL16" t="n">
         <v>0.9982064962387085</v>
       </c>
       <c r="AM16" t="n">
-        <v>239.2780790937708</v>
+        <v>20.97216667012965</v>
       </c>
       <c r="AN16" t="n">
         <v>12.20057061377992</v>
@@ -3685,7 +3685,7 @@
         <v>0.9981188476085663</v>
       </c>
       <c r="AP16" t="n">
-        <v>203.2626253493289</v>
+        <v>-14.16785463373712</v>
       </c>
       <c r="AQ16" t="n">
         <v>20.47148359582779</v>
@@ -3694,7 +3694,7 @@
         <v>0.953741192817688</v>
       </c>
       <c r="AS16" t="n">
-        <v>166.6552036366564</v>
+        <v>-51.11450844622674</v>
       </c>
       <c r="AT16" t="n">
         <v>34.43954143118351</v>
@@ -3703,61 +3703,61 @@
         <v>0.987178236246109</v>
       </c>
       <c r="AV16" t="n">
-        <v>67.56746793542175</v>
+        <v>0.02490916150681244</v>
       </c>
       <c r="AW16" t="n">
-        <v>66.26126212514227</v>
+        <v>-0.02994334444086633</v>
       </c>
       <c r="AX16" t="n">
-        <v>84.96347016024515</v>
+        <v>0.1268254949691467</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.02490916150681244</v>
+        <v>-0.1113206782239615</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0.02994334444086633</v>
+        <v>0.3386233715300762</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.1268254949691396</v>
+        <v>-0.07396353052018156</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0.1113206782239615</v>
+        <v>0.5455849018502832</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.3386233715300904</v>
+        <v>0.0649888464745132</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0.07396353052017446</v>
+        <v>0.8622717350087186</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.5455849018502761</v>
+        <v>0.3246652319076233</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.06498884647450609</v>
+        <v>66.02852416939172</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.8622717350087328</v>
+        <v>64.76847338785271</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.3246652319076304</v>
+        <v>85.91255905499449</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0.3466796462302888</v>
+        <v>-0.2979064253758565</v>
       </c>
       <c r="BJ16" t="n">
-        <v>-0.4454074354836433</v>
+        <v>-0.4408705384416507</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0.3668698062256901</v>
+        <v>-0.3127061870843626</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.027679918296746</v>
+        <v>1.059835870614389</v>
       </c>
       <c r="BM16" t="n">
-        <v>-1.035010164784051</v>
+        <v>-1.033469947049063</v>
       </c>
       <c r="BN16" t="n">
-        <v>-0.5298679325662832</v>
+        <v>-0.5145943187331863</v>
       </c>
     </row>
     <row r="17">
@@ -3768,16 +3768,16 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>314.0119364921082</v>
+        <v>95.54794950688139</v>
       </c>
       <c r="D17" t="n">
-        <v>7.028190125810326</v>
+        <v>7.028190125810339</v>
       </c>
       <c r="E17" t="n">
         <v>0.06585794501006603</v>
       </c>
       <c r="F17" t="n">
-        <v>317.3210383729732</v>
+        <v>98.35146602163923</v>
       </c>
       <c r="G17" t="n">
         <v>17.53658538169049</v>
@@ -3786,25 +3786,25 @@
         <v>0.9901688992977142</v>
       </c>
       <c r="I17" t="n">
-        <v>316.5016945372237</v>
+        <v>98.90021872013173</v>
       </c>
       <c r="J17" t="n">
-        <v>6.695718968168208</v>
+        <v>6.695718968168219</v>
       </c>
       <c r="K17" t="n">
         <v>0.9609758853912354</v>
       </c>
       <c r="L17" t="n">
-        <v>313.0567791614126</v>
+        <v>94.27615607038456</v>
       </c>
       <c r="M17" t="n">
-        <v>8.04040787067818</v>
+        <v>8.040407870678191</v>
       </c>
       <c r="N17" t="n">
         <v>0.9796699583530426</v>
       </c>
       <c r="O17" t="n">
-        <v>301.9379209964834</v>
+        <v>82.83364924978704</v>
       </c>
       <c r="P17" t="n">
         <v>13.90990399299784</v>
@@ -3813,7 +3813,7 @@
         <v>0.9815521538257599</v>
       </c>
       <c r="R17" t="n">
-        <v>307.4531570393989</v>
+        <v>89.64864193124973</v>
       </c>
       <c r="S17" t="n">
         <v>18.41536988603308</v>
@@ -3822,7 +3822,7 @@
         <v>0.9943571984767914</v>
       </c>
       <c r="U17" t="n">
-        <v>303.1330438370401</v>
+        <v>84.84784440791353</v>
       </c>
       <c r="V17" t="n">
         <v>25.41022605084358</v>
@@ -3831,16 +3831,16 @@
         <v>0.9815084040164948</v>
       </c>
       <c r="X17" t="n">
-        <v>258.5973090313851</v>
+        <v>41.39298378153049</v>
       </c>
       <c r="Y17" t="n">
-        <v>22.31517548256731</v>
+        <v>22.31517548256732</v>
       </c>
       <c r="Z17" t="n">
         <v>0.9876958131790161</v>
       </c>
       <c r="AA17" t="n">
-        <v>254.3466912939193</v>
+        <v>37.2545343764285</v>
       </c>
       <c r="AB17" t="n">
         <v>14.1635813611619</v>
@@ -3849,34 +3849,34 @@
         <v>0.993973433971405</v>
       </c>
       <c r="AD17" t="n">
-        <v>263.5999415783173</v>
+        <v>46.3352304823855</v>
       </c>
       <c r="AE17" t="n">
-        <v>10.391462610123</v>
+        <v>10.39146261012301</v>
       </c>
       <c r="AF17" t="n">
         <v>0.9814404845237732</v>
       </c>
       <c r="AG17" t="n">
-        <v>254.6119811687064</v>
+        <v>36.80246637222614</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.376634963015277</v>
+        <v>1.376634963015293</v>
       </c>
       <c r="AI17" t="n">
         <v>0.9966603219509125</v>
       </c>
       <c r="AJ17" t="n">
-        <v>261.8320201305633</v>
+        <v>43.92153760220143</v>
       </c>
       <c r="AK17" t="n">
-        <v>-1.391325605676528</v>
+        <v>-1.391325605676529</v>
       </c>
       <c r="AL17" t="n">
         <v>0.9980300962924957</v>
       </c>
       <c r="AM17" t="n">
-        <v>241.0073787608046</v>
+        <v>22.7014663371634</v>
       </c>
       <c r="AN17" t="n">
         <v>12.53563901211353</v>
@@ -3885,7 +3885,7 @@
         <v>0.998477429151535</v>
       </c>
       <c r="AP17" t="n">
-        <v>205.4523589763236</v>
+        <v>-11.97812100674244</v>
       </c>
       <c r="AQ17" t="n">
         <v>20.50553179801778</v>
@@ -3894,7 +3894,7 @@
         <v>0.9493388831615448</v>
       </c>
       <c r="AS17" t="n">
-        <v>169.5460461555643</v>
+        <v>-48.22366592731883</v>
       </c>
       <c r="AT17" t="n">
         <v>34.00145591573512</v>
@@ -3903,61 +3903,61 @@
         <v>0.9860702455043793</v>
       </c>
       <c r="AV17" t="n">
-        <v>66.03274162389832</v>
+        <v>-0.0548596077777006</v>
       </c>
       <c r="AW17" t="n">
-        <v>67.28512350941132</v>
+        <v>-0.02938686533177304</v>
       </c>
       <c r="AX17" t="n">
-        <v>84.67556537334872</v>
+        <v>-0.04067826778331352</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.05485960777768639</v>
+        <v>0.07433231840743204</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0.02938686533176593</v>
+        <v>0.4447216683245756</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.04067826778331352</v>
+        <v>0.2569092080948323</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.07433231840743204</v>
+        <v>0.7730717354632333</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.4447216683245614</v>
+        <v>0.2367116035298942</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.2569092080948181</v>
+        <v>0.8133533153128241</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.7730717354632404</v>
+        <v>-0.06552706373498296</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.2367116035299084</v>
+        <v>64.61995445312257</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.8133533153128099</v>
+        <v>65.98213988133386</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.06552706373499717</v>
+        <v>85.67940498941496</v>
       </c>
       <c r="BI17" t="n">
-        <v>-1.367151887131067</v>
+        <v>-1.257459100929916</v>
       </c>
       <c r="BJ17" t="n">
-        <v>-0.4742482928226641</v>
+        <v>-0.4271926709450398</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0.4444965987374658</v>
+        <v>-0.3047803630817221</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0.9154092916595644</v>
+        <v>-0.878078040171987</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.375230397154091</v>
+        <v>2.419242892991765</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.969190052541444</v>
+        <v>1.979934868403383</v>
       </c>
     </row>
     <row r="18">
@@ -3968,70 +3968,70 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>315.8174730361776</v>
+        <v>97.35348605095072</v>
       </c>
       <c r="D18" t="n">
-        <v>5.102287454808007</v>
+        <v>5.102287454808012</v>
       </c>
       <c r="E18" t="n">
         <v>0.06742413341999054</v>
       </c>
       <c r="F18" t="n">
-        <v>319.1004312418877</v>
+        <v>100.1308588905537</v>
       </c>
       <c r="G18" t="n">
-        <v>17.63343811035155</v>
+        <v>17.63343811035156</v>
       </c>
       <c r="H18" t="n">
         <v>0.9876008927822113</v>
       </c>
       <c r="I18" t="n">
-        <v>318.3291629273841</v>
+        <v>100.7276871102922</v>
       </c>
       <c r="J18" t="n">
-        <v>4.752301155252653</v>
+        <v>4.75230115525266</v>
       </c>
       <c r="K18" t="n">
         <v>0.9636979401111603</v>
       </c>
       <c r="L18" t="n">
-        <v>314.8150134593882</v>
+        <v>96.03439036836016</v>
       </c>
       <c r="M18" t="n">
-        <v>6.157895351978055</v>
+        <v>6.157895351978059</v>
       </c>
       <c r="N18" t="n">
         <v>0.9908323287963867</v>
       </c>
       <c r="O18" t="n">
-        <v>304.7550099961301</v>
+        <v>85.6507382494338</v>
       </c>
       <c r="P18" t="n">
-        <v>13.3217101401471</v>
+        <v>13.32171014014711</v>
       </c>
       <c r="Q18" t="n">
         <v>0.9834110140800476</v>
       </c>
       <c r="R18" t="n">
-        <v>309.8515982323505</v>
+        <v>92.04708312420135</v>
       </c>
       <c r="S18" t="n">
-        <v>17.92411804199217</v>
+        <v>17.92411804199219</v>
       </c>
       <c r="T18" t="n">
         <v>0.9933597445487976</v>
       </c>
       <c r="U18" t="n">
-        <v>306.3317268452746</v>
+        <v>88.04652741614808</v>
       </c>
       <c r="V18" t="n">
-        <v>25.23980647959607</v>
+        <v>25.23980647959608</v>
       </c>
       <c r="W18" t="n">
         <v>0.9885892868041992</v>
       </c>
       <c r="X18" t="n">
-        <v>260.343592217628</v>
+        <v>43.13926696777344</v>
       </c>
       <c r="Y18" t="n">
         <v>22.09303835605053</v>
@@ -4040,124 +4040,124 @@
         <v>0.9911301136016846</v>
       </c>
       <c r="AA18" t="n">
-        <v>256.5510993308209</v>
+        <v>39.45894241333005</v>
       </c>
       <c r="AB18" t="n">
-        <v>13.64981468687665</v>
+        <v>13.64981468687666</v>
       </c>
       <c r="AC18" t="n">
         <v>0.9816303253173828</v>
       </c>
       <c r="AD18" t="n">
-        <v>265.1886879129613</v>
+        <v>47.9239768170296</v>
       </c>
       <c r="AE18" t="n">
-        <v>9.366266778174847</v>
+        <v>9.366266778174868</v>
       </c>
       <c r="AF18" t="n">
         <v>0.9886771738529205</v>
       </c>
       <c r="AG18" t="n">
-        <v>254.916958098716</v>
+        <v>37.10744330223571</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.280431544527076</v>
+        <v>1.280431544527095</v>
       </c>
       <c r="AI18" t="n">
         <v>0.9960010647773743</v>
       </c>
       <c r="AJ18" t="n">
-        <v>261.6163476984552</v>
+        <v>43.70586517009329</v>
       </c>
       <c r="AK18" t="n">
-        <v>-1.750069476188514</v>
+        <v>-1.750069476188497</v>
       </c>
       <c r="AL18" t="n">
         <v>0.9988548457622528</v>
       </c>
       <c r="AM18" t="n">
-        <v>243.2602050456595</v>
+        <v>24.95429262201836</v>
       </c>
       <c r="AN18" t="n">
-        <v>12.43474432762632</v>
+        <v>12.43474432762633</v>
       </c>
       <c r="AO18" t="n">
         <v>0.99898561835289</v>
       </c>
       <c r="AP18" t="n">
-        <v>208.2046549370948</v>
+        <v>-9.225825045971163</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20.82406713607462</v>
+        <v>20.82406713607464</v>
       </c>
       <c r="AR18" t="n">
         <v>0.9546061456203461</v>
       </c>
       <c r="AS18" t="n">
-        <v>172.7939118730261</v>
+        <v>-44.97580020985706</v>
       </c>
       <c r="AT18" t="n">
-        <v>34.39051039675448</v>
+        <v>34.39051039675449</v>
       </c>
       <c r="AU18" t="n">
         <v>0.986187219619751</v>
       </c>
       <c r="AV18" t="n">
-        <v>62.60102214108424</v>
+        <v>-0.1792948296729548</v>
       </c>
       <c r="AW18" t="n">
-        <v>64.64734772704212</v>
+        <v>0.02259700856310332</v>
       </c>
       <c r="AX18" t="n">
-        <v>92.26442079661805</v>
+        <v>0.1725430184222461</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.1792948296729548</v>
+        <v>-0.1174272374903929</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.02259700856309621</v>
+        <v>0.499385468503263</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.172543018422239</v>
+        <v>-0.3801112479352042</v>
       </c>
       <c r="BB18" t="n">
-        <v>-0.1174272374903964</v>
+        <v>1.089620590209961</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.4993854685032773</v>
+        <v>-0.1795905701657361</v>
       </c>
       <c r="BD18" t="n">
-        <v>-0.38011124793519</v>
+        <v>0.8494782955088453</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.089620590209968</v>
+        <v>0.07862689647268439</v>
       </c>
       <c r="BF18" t="n">
-        <v>-0.1795905701657574</v>
+        <v>61.50261405307329</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.8494782955088453</v>
+        <v>63.68349421412709</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.0786268964726915</v>
+        <v>93.365990397449</v>
       </c>
       <c r="BI18" t="n">
-        <v>-0.4386303606237991</v>
+        <v>-0.3083919547225662</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.6602849971737639</v>
+        <v>0.6465208207346427</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0.05973230239369443</v>
+        <v>0.1001333068338361</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.732393753682933</v>
+        <v>0.7448004416522007</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.680694149370421</v>
+        <v>4.75823481146638</v>
       </c>
       <c r="BN18" t="n">
-        <v>-0.2738244428174319</v>
+        <v>-0.2626719155429367</v>
       </c>
     </row>
     <row r="19">
@@ -4168,61 +4168,61 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>316.0766469671371</v>
+        <v>97.61265998191021</v>
       </c>
       <c r="D19" t="n">
-        <v>4.042199317445139</v>
+        <v>4.042199317445147</v>
       </c>
       <c r="E19" t="n">
         <v>0.1018488667905331</v>
       </c>
       <c r="F19" t="n">
-        <v>320.0765143049525</v>
+        <v>101.1069419536185</v>
       </c>
       <c r="G19" t="n">
-        <v>16.76742066728306</v>
+        <v>16.76742066728308</v>
       </c>
       <c r="H19" t="n">
         <v>0.8972715437412262</v>
       </c>
       <c r="I19" t="n">
-        <v>317.8510067310739</v>
+        <v>100.249530913982</v>
       </c>
       <c r="J19" t="n">
-        <v>3.649431593874652</v>
+        <v>3.649431593874668</v>
       </c>
       <c r="K19" t="n">
         <v>0.9867721796035767</v>
       </c>
       <c r="L19" t="n">
-        <v>314.9142026901245</v>
+        <v>96.13357959909641</v>
       </c>
       <c r="M19" t="n">
-        <v>5.470860258061819</v>
+        <v>5.470860258061835</v>
       </c>
       <c r="N19" t="n">
         <v>0.9941810667514801</v>
       </c>
       <c r="O19" t="n">
-        <v>306.1784439898552</v>
+        <v>87.07417224315887</v>
       </c>
       <c r="P19" t="n">
-        <v>13.49863904587765</v>
+        <v>13.49863904587766</v>
       </c>
       <c r="Q19" t="n">
         <v>0.9755373001098633</v>
       </c>
       <c r="R19" t="n">
-        <v>311.8735896780136</v>
+        <v>94.06907456986445</v>
       </c>
       <c r="S19" t="n">
-        <v>17.70836038792386</v>
+        <v>17.70836038792387</v>
       </c>
       <c r="T19" t="n">
         <v>0.9893573224544525</v>
       </c>
       <c r="U19" t="n">
-        <v>308.0976876806706</v>
+        <v>89.81248825154407</v>
       </c>
       <c r="V19" t="n">
         <v>25.00137978411735</v>
@@ -4231,7 +4231,7 @@
         <v>0.9848753809928894</v>
       </c>
       <c r="X19" t="n">
-        <v>262.4043829897616</v>
+        <v>45.20005773990712</v>
       </c>
       <c r="Y19" t="n">
         <v>21.8157504467254</v>
@@ -4240,34 +4240,34 @@
         <v>0.9906715750694275</v>
       </c>
       <c r="AA19" t="n">
-        <v>258.0371450870595</v>
+        <v>40.94498816956866</v>
       </c>
       <c r="AB19" t="n">
-        <v>13.03872453405504</v>
+        <v>13.03872453405502</v>
       </c>
       <c r="AC19" t="n">
         <v>0.9879297316074371</v>
       </c>
       <c r="AD19" t="n">
-        <v>265.2569892558646</v>
+        <v>47.99227815993288</v>
       </c>
       <c r="AE19" t="n">
-        <v>7.97153229409075</v>
+        <v>7.971532294090759</v>
       </c>
       <c r="AF19" t="n">
         <v>0.9784060716629028</v>
       </c>
       <c r="AG19" t="n">
-        <v>254.752226078764</v>
+        <v>36.94271128228371</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.923873576712097</v>
+        <v>1.923873576712101</v>
       </c>
       <c r="AI19" t="n">
         <v>0.9969601631164551</v>
       </c>
       <c r="AJ19" t="n">
-        <v>261.4910633005994</v>
+        <v>43.58058077223757</v>
       </c>
       <c r="AK19" t="n">
         <v>-2.283664459877826</v>
@@ -4276,7 +4276,7 @@
         <v>0.9990509152412415</v>
       </c>
       <c r="AM19" t="n">
-        <v>245.796341591693</v>
+        <v>27.49042916805186</v>
       </c>
       <c r="AN19" t="n">
         <v>12.29850282060339</v>
@@ -4285,79 +4285,79 @@
         <v>0.999478667974472</v>
       </c>
       <c r="AP19" t="n">
-        <v>211.5862055027739</v>
+        <v>-5.844274480292142</v>
       </c>
       <c r="AQ19" t="n">
-        <v>21.19298894354638</v>
+        <v>21.19298894354637</v>
       </c>
       <c r="AR19" t="n">
         <v>0.9584556519985199</v>
       </c>
       <c r="AS19" t="n">
-        <v>177.1372693650266</v>
+        <v>-40.63244271785655</v>
       </c>
       <c r="AT19" t="n">
-        <v>34.93237191058221</v>
+        <v>34.9323719105822</v>
       </c>
       <c r="AU19" t="n">
         <v>0.9926108717918396</v>
       </c>
       <c r="AV19" t="n">
-        <v>61.81044264696521</v>
+        <v>-0.03924775630869703</v>
       </c>
       <c r="AW19" t="n">
-        <v>64.93914695940464</v>
+        <v>-0.03331925006622782</v>
       </c>
       <c r="AX19" t="n">
-        <v>98.75797844861768</v>
+        <v>-0.2618667927194238</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0.03924775630871125</v>
+        <v>-0.04874746850196487</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0.03331925006623493</v>
+        <v>0.3038477390370531</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0.2618667927194238</v>
+        <v>0.3058027713856859</v>
       </c>
       <c r="BB19" t="n">
-        <v>-0.04874746850196132</v>
+        <v>0.693148755012686</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.3038477390370389</v>
+        <v>0.04926742391382533</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.3058027713856717</v>
+        <v>1.408760598365291</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.6931487550126718</v>
+        <v>0.02531193672341914</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.04926742391383598</v>
+        <v>60.97135693596258</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.408760598365305</v>
+        <v>64.36405031352911</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.02531193672343335</v>
+        <v>100.0018881433113</v>
       </c>
       <c r="BI19" t="n">
-        <v>-2.19809052702408</v>
+        <v>-1.95181678639311</v>
       </c>
       <c r="BJ19" t="n">
-        <v>-1.126647539876998</v>
+        <v>-1.035466115007337</v>
       </c>
       <c r="BK19" t="n">
-        <v>-2.617852973557618</v>
+        <v>-2.31961651854685</v>
       </c>
       <c r="BL19" t="n">
-        <v>-1.929173998812823</v>
+        <v>-1.859906638190199</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.6368761716824558</v>
+        <v>0.6589583953734603</v>
       </c>
       <c r="BN19" t="n">
-        <v>-0.7660591584254028</v>
+        <v>-0.7868015568575082</v>
       </c>
     </row>
     <row r="20">
@@ -4368,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>316.1978521245591</v>
+        <v>97.73386513933221</v>
       </c>
       <c r="D20" t="n">
         <v>4.494760391560007</v>
@@ -4377,34 +4377,34 @@
         <v>0.05918348953127861</v>
       </c>
       <c r="F20" t="n">
-        <v>320.8707796766403</v>
+        <v>101.9012073253063</v>
       </c>
       <c r="G20" t="n">
-        <v>17.06904147533662</v>
+        <v>17.0690414753366</v>
       </c>
       <c r="H20" t="n">
         <v>0.572317436337471</v>
       </c>
       <c r="I20" t="n">
-        <v>317.9103349117522</v>
+        <v>100.3088590946603</v>
       </c>
       <c r="J20" t="n">
-        <v>4.003938715508653</v>
+        <v>4.003938715508644</v>
       </c>
       <c r="K20" t="n">
         <v>0.9848985075950623</v>
       </c>
       <c r="L20" t="n">
-        <v>315.1363043074912</v>
+        <v>96.35568121646313</v>
       </c>
       <c r="M20" t="n">
-        <v>6.021191211456951</v>
+        <v>6.021191211456949</v>
       </c>
       <c r="N20" t="n">
         <v>0.9948025643825531</v>
       </c>
       <c r="O20" t="n">
-        <v>308.3101480565173</v>
+        <v>89.20587630982095</v>
       </c>
       <c r="P20" t="n">
         <v>14.48380490566822</v>
@@ -4413,7 +4413,7 @@
         <v>0.962165892124176</v>
       </c>
       <c r="R20" t="n">
-        <v>313.5824464737101</v>
+        <v>95.77793136556099</v>
       </c>
       <c r="S20" t="n">
         <v>18.11098950974485</v>
@@ -4422,16 +4422,16 @@
         <v>0.9857887923717499</v>
       </c>
       <c r="U20" t="n">
-        <v>310.2134653862487</v>
+        <v>91.92826595712214</v>
       </c>
       <c r="V20" t="n">
-        <v>25.61177192850317</v>
+        <v>25.61177192850316</v>
       </c>
       <c r="W20" t="n">
         <v>0.9793627262115479</v>
       </c>
       <c r="X20" t="n">
-        <v>264.5664215087891</v>
+        <v>47.36209625893449</v>
       </c>
       <c r="Y20" t="n">
         <v>21.71324871956034</v>
@@ -4440,16 +4440,16 @@
         <v>0.9891479313373566</v>
       </c>
       <c r="AA20" t="n">
-        <v>259.7202605389534</v>
+        <v>42.62810362146257</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.22810396235039</v>
+        <v>13.2281039623504</v>
       </c>
       <c r="AC20" t="n">
         <v>0.9842883944511414</v>
       </c>
       <c r="AD20" t="n">
-        <v>266.5485016843106</v>
+        <v>49.28379058837891</v>
       </c>
       <c r="AE20" t="n">
         <v>7.104589584025931</v>
@@ -4458,25 +4458,25 @@
         <v>0.9849129915237427</v>
       </c>
       <c r="AG20" t="n">
-        <v>254.3925041848041</v>
+        <v>36.58298938832385</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.700434907953792</v>
+        <v>3.70043490795379</v>
       </c>
       <c r="AI20" t="n">
         <v>0.9936885833740234</v>
       </c>
       <c r="AJ20" t="n">
-        <v>261.2325019024788</v>
+        <v>43.32201937411693</v>
       </c>
       <c r="AK20" t="n">
-        <v>-2.222126088243854</v>
+        <v>-2.22212608824385</v>
       </c>
       <c r="AL20" t="n">
         <v>0.9991549253463745</v>
       </c>
       <c r="AM20" t="n">
-        <v>248.3702963971077</v>
+        <v>30.06438397346658</v>
       </c>
       <c r="AN20" t="n">
         <v>12.12323777219082</v>
@@ -4485,16 +4485,16 @@
         <v>0.9992724657058716</v>
       </c>
       <c r="AP20" t="n">
-        <v>216.0727602370242</v>
+        <v>-1.357719746041809</v>
       </c>
       <c r="AQ20" t="n">
-        <v>21.12687293519366</v>
+        <v>21.12687293519365</v>
       </c>
       <c r="AR20" t="n">
         <v>0.9680086374282837</v>
       </c>
       <c r="AS20" t="n">
-        <v>184.0270468529234</v>
+        <v>-33.7426652299597</v>
       </c>
       <c r="AT20" t="n">
         <v>34.45054318042511</v>
@@ -4503,61 +4503,61 @@
         <v>0.9964641332626343</v>
       </c>
       <c r="AV20" t="n">
-        <v>56.51327299333821</v>
+        <v>-0.05740815020621426</v>
       </c>
       <c r="AW20" t="n">
-        <v>57.51425019651588</v>
+        <v>0.06686119323081385</v>
       </c>
       <c r="AX20" t="n">
-        <v>102.1872994669157</v>
+        <v>0.06048425715020045</v>
       </c>
       <c r="AY20" t="n">
-        <v>-0.05740815020621426</v>
+        <v>0.1842721979668731</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.06686119323082096</v>
+        <v>0.478330571600722</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.06048425715020755</v>
+        <v>-0.1104420803962896</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.1842721979668838</v>
+        <v>1.088987512791405</v>
       </c>
       <c r="BC20" t="n">
-        <v>0.478330571600722</v>
+        <v>0.159819075401785</v>
       </c>
       <c r="BD20" t="n">
-        <v>-0.1104420803962824</v>
+        <v>0.6960980435635236</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.088987512791405</v>
+        <v>-0.02938990897319371</v>
       </c>
       <c r="BF20" t="n">
-        <v>0.159819075401785</v>
+        <v>56.29823535882251</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.6960980435635236</v>
+        <v>57.60497986017033</v>
       </c>
       <c r="BH20" t="n">
-        <v>-0.02938990897322213</v>
+        <v>103.4905796617435</v>
       </c>
       <c r="BI20" t="n">
-        <v>-2.475770992945566</v>
+        <v>-2.222089526760511</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.5593260358723491</v>
+        <v>0.5010321916474307</v>
       </c>
       <c r="BK20" t="n">
-        <v>-0.1967502535208396</v>
+        <v>0.1166016588719163</v>
       </c>
       <c r="BL20" t="n">
-        <v>2.57764564549776</v>
+        <v>2.542824772375806</v>
       </c>
       <c r="BM20" t="n">
-        <v>6.669427118703521</v>
+        <v>6.780334496727459</v>
       </c>
       <c r="BN20" t="n">
-        <v>2.138190190690535</v>
+        <v>2.172348058115736</v>
       </c>
     </row>
     <row r="21">
@@ -4568,133 +4568,133 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>316.2069867265985</v>
+        <v>97.74299974137165</v>
       </c>
       <c r="D21" t="n">
-        <v>4.184787831407903</v>
+        <v>4.184787831407912</v>
       </c>
       <c r="E21" t="n">
         <v>0.04889192245900631</v>
       </c>
       <c r="F21" t="n">
-        <v>321.2350962009836</v>
+        <v>102.2655238496496</v>
       </c>
       <c r="G21" t="n">
-        <v>17.47213323065574</v>
+        <v>17.47213323065575</v>
       </c>
       <c r="H21" t="n">
         <v>0.1868381835520267</v>
       </c>
       <c r="I21" t="n">
-        <v>318.0556384806937</v>
+        <v>100.4541626636018</v>
       </c>
       <c r="J21" t="n">
-        <v>3.921387043405076</v>
+        <v>3.921387043405087</v>
       </c>
       <c r="K21" t="n">
         <v>0.9701146483421326</v>
       </c>
       <c r="L21" t="n">
-        <v>315.5863848138363</v>
+        <v>96.8057617228082</v>
       </c>
       <c r="M21" t="n">
-        <v>5.985868738052687</v>
+        <v>5.985868738052693</v>
       </c>
       <c r="N21" t="n">
         <v>0.9937803447246552</v>
       </c>
       <c r="O21" t="n">
-        <v>310.7434166238663</v>
+        <v>91.63914487716997</v>
       </c>
       <c r="P21" t="n">
-        <v>14.96788998867602</v>
+        <v>14.96788998867603</v>
       </c>
       <c r="Q21" t="n">
         <v>0.9559946060180664</v>
       </c>
       <c r="R21" t="n">
-        <v>315.5805805896191</v>
+        <v>97.77606548147</v>
       </c>
       <c r="S21" t="n">
-        <v>18.39071233221824</v>
+        <v>18.39071233221825</v>
       </c>
       <c r="T21" t="n">
         <v>0.9820043444633484</v>
       </c>
       <c r="U21" t="n">
-        <v>311.8439088476465</v>
+        <v>93.55870941852001</v>
       </c>
       <c r="V21" t="n">
-        <v>25.93869960054437</v>
+        <v>25.93869960054438</v>
       </c>
       <c r="W21" t="n">
         <v>0.9482457339763641</v>
       </c>
       <c r="X21" t="n">
-        <v>266.6109003919236</v>
+        <v>49.40657514206907</v>
       </c>
       <c r="Y21" t="n">
-        <v>21.76824529120263</v>
+        <v>21.76824529120262</v>
       </c>
       <c r="Z21" t="n">
         <v>0.9929049015045166</v>
       </c>
       <c r="AA21" t="n">
-        <v>262.0426522924545</v>
+        <v>44.95049537496362</v>
       </c>
       <c r="AB21" t="n">
-        <v>13.74505225648272</v>
+        <v>13.74505225648271</v>
       </c>
       <c r="AC21" t="n">
         <v>0.9888351559638977</v>
       </c>
       <c r="AD21" t="n">
-        <v>267.3982457911715</v>
+        <v>50.13353469523977</v>
       </c>
       <c r="AE21" t="n">
-        <v>6.449305757563167</v>
+        <v>6.449305757563165</v>
       </c>
       <c r="AF21" t="n">
         <v>0.9891807436943054</v>
       </c>
       <c r="AG21" t="n">
-        <v>254.7698710827118</v>
+        <v>36.96035628623149</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.9727257261885</v>
+        <v>4.972725726188498</v>
       </c>
       <c r="AI21" t="n">
         <v>0.9970900416374207</v>
       </c>
       <c r="AJ21" t="n">
-        <v>261.2413852772814</v>
+        <v>43.33090274891956</v>
       </c>
       <c r="AK21" t="n">
-        <v>-1.908695951421208</v>
+        <v>-1.90869595142121</v>
       </c>
       <c r="AL21" t="n">
         <v>0.9989767372608185</v>
       </c>
       <c r="AM21" t="n">
-        <v>250.7913751805082</v>
+        <v>32.48546275686709</v>
       </c>
       <c r="AN21" t="n">
-        <v>13.0090429427776</v>
+        <v>13.00904294277759</v>
       </c>
       <c r="AO21" t="n">
         <v>0.9996229708194733</v>
       </c>
       <c r="AP21" t="n">
-        <v>220.1978764635451</v>
+        <v>2.767396480479135</v>
       </c>
       <c r="AQ21" t="n">
-        <v>20.9358702314661</v>
+        <v>20.93587023146609</v>
       </c>
       <c r="AR21" t="n">
         <v>0.9753628373146057</v>
       </c>
       <c r="AS21" t="n">
-        <v>190.742987774788</v>
+        <v>-27.02672430809508</v>
       </c>
       <c r="AT21" t="n">
         <v>33.84694850191157</v>
@@ -4703,61 +4703,61 @@
         <v>0.9931918680667877</v>
       </c>
       <c r="AV21" t="n">
-        <v>53.45340748320059</v>
+        <v>-0.07359220626507579</v>
       </c>
       <c r="AW21" t="n">
-        <v>60.39993601561815</v>
+        <v>-0.06934328282133606</v>
       </c>
       <c r="AX21" t="n">
-        <v>114.1693812479758</v>
+        <v>0.3551706354668767</v>
       </c>
       <c r="AY21" t="n">
-        <v>-0.07359220626506158</v>
+        <v>0.1112750236024382</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.06934328282132896</v>
+        <v>0.5777369154260583</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.3551706354668838</v>
+        <v>0.03291748939676609</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.1112750236024169</v>
+        <v>0.864292712921781</v>
       </c>
       <c r="BC21" t="n">
-        <v>0.5777369154260583</v>
+        <v>-0.1663370335355623</v>
       </c>
       <c r="BD21" t="n">
-        <v>0.03291748939676609</v>
+        <v>1.337510981458294</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.8642927129217952</v>
+        <v>-0.01374965018415963</v>
       </c>
       <c r="BF21" t="n">
-        <v>-0.1663370335355552</v>
+        <v>53.62924254827217</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.337510981458294</v>
+        <v>61.01720849631478</v>
       </c>
       <c r="BH21" t="n">
-        <v>-0.01374965018413121</v>
+        <v>115.6686634126387</v>
       </c>
       <c r="BI21" t="n">
-        <v>0.3619548359481186</v>
+        <v>0.5078733148438097</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1.246555733350429</v>
+        <v>1.206011187393501</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.5962816427267903</v>
+        <v>0.7271124290582112</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.09703550615430867</v>
+        <v>0.008589151495667302</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.4435027609419002</v>
+        <v>0.4322010408905861</v>
       </c>
       <c r="BN21" t="n">
-        <v>-1.862763864427638</v>
+        <v>-1.910840329521582</v>
       </c>
     </row>
     <row r="22">
@@ -4768,16 +4768,16 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>256.6238730511766</v>
+        <v>38.15988606594978</v>
       </c>
       <c r="D22" t="n">
-        <v>21.29589243138091</v>
+        <v>21.2958924313809</v>
       </c>
       <c r="E22" t="n">
         <v>0.02502510044723749</v>
       </c>
       <c r="F22" t="n">
-        <v>320.6390042888357</v>
+        <v>101.6694319375018</v>
       </c>
       <c r="G22" t="n">
         <v>19.81951936762384</v>
@@ -4786,52 +4786,52 @@
         <v>0.03844720963388681</v>
       </c>
       <c r="I22" t="n">
-        <v>318.1405355955692</v>
+        <v>100.5390597784773</v>
       </c>
       <c r="J22" t="n">
-        <v>3.609539600128826</v>
+        <v>3.609539600128823</v>
       </c>
       <c r="K22" t="n">
         <v>0.9827839434146881</v>
       </c>
       <c r="L22" t="n">
-        <v>315.5370874607817</v>
+        <v>96.75646436975356</v>
       </c>
       <c r="M22" t="n">
-        <v>5.735754459462271</v>
+        <v>5.735754459462267</v>
       </c>
       <c r="N22" t="n">
         <v>0.9952089190483093</v>
       </c>
       <c r="O22" t="n">
-        <v>311.8092760126642</v>
+        <v>92.70500426596783</v>
       </c>
       <c r="P22" t="n">
-        <v>14.42188506430769</v>
+        <v>14.42188506430768</v>
       </c>
       <c r="Q22" t="n">
         <v>0.9672504961490631</v>
       </c>
       <c r="R22" t="n">
-        <v>317.357970996106</v>
+        <v>99.5534558879568</v>
       </c>
       <c r="S22" t="n">
-        <v>18.13339882708611</v>
+        <v>18.1333988270861</v>
       </c>
       <c r="T22" t="n">
         <v>0.7365812957286835</v>
       </c>
       <c r="U22" t="n">
-        <v>315.0424538774694</v>
+        <v>96.75725444834285</v>
       </c>
       <c r="V22" t="n">
-        <v>25.31051635742189</v>
+        <v>25.31051635742188</v>
       </c>
       <c r="W22" t="n">
         <v>0.7576433122158051</v>
       </c>
       <c r="X22" t="n">
-        <v>268.6003806743216</v>
+        <v>51.39605542446702</v>
       </c>
       <c r="Y22" t="n">
         <v>22.23393866356383</v>
@@ -4840,7 +4840,7 @@
         <v>0.9876590073108673</v>
       </c>
       <c r="AA22" t="n">
-        <v>263.6996959118133</v>
+        <v>46.60753899432243</v>
       </c>
       <c r="AB22" t="n">
         <v>14.43110526876247</v>
@@ -4849,7 +4849,7 @@
         <v>0.9923707544803619</v>
       </c>
       <c r="AD22" t="n">
-        <v>268.3796598556194</v>
+        <v>51.11494875968771</v>
       </c>
       <c r="AE22" t="n">
         <v>6.071942917844083</v>
@@ -4858,34 +4858,34 @@
         <v>0.9896419048309326</v>
       </c>
       <c r="AG22" t="n">
-        <v>255.5923380750291</v>
+        <v>37.78282327854888</v>
       </c>
       <c r="AH22" t="n">
-        <v>5.427518804022611</v>
+        <v>5.427518804022607</v>
       </c>
       <c r="AI22" t="n">
         <v>0.9975069165229797</v>
       </c>
       <c r="AJ22" t="n">
-        <v>260.9728955207987</v>
+        <v>43.06241299243683</v>
       </c>
       <c r="AK22" t="n">
-        <v>-1.585582976645611</v>
+        <v>-1.585582976645612</v>
       </c>
       <c r="AL22" t="n">
         <v>0.9985335767269135</v>
       </c>
       <c r="AM22" t="n">
-        <v>252.6078102436472</v>
+        <v>34.30189782000603</v>
       </c>
       <c r="AN22" t="n">
-        <v>13.90645453270446</v>
+        <v>13.90645453270445</v>
       </c>
       <c r="AO22" t="n">
         <v>0.9994244277477264</v>
       </c>
       <c r="AP22" t="n">
-        <v>223.6591055038128</v>
+        <v>6.228625520746746</v>
       </c>
       <c r="AQ22" t="n">
         <v>22.25408351167719</v>
@@ -4894,7 +4894,7 @@
         <v>0.9788185358047485</v>
       </c>
       <c r="AS22" t="n">
-        <v>195.6364164961145</v>
+        <v>-22.13329558676863</v>
       </c>
       <c r="AT22" t="n">
         <v>34.90946749423413</v>
@@ -4903,61 +4903,61 @@
         <v>0.9901745021343231</v>
       </c>
       <c r="AV22" t="n">
-        <v>55.37976490646469</v>
+        <v>-0.1373057669781446</v>
       </c>
       <c r="AW22" t="n">
-        <v>63.67376385933767</v>
+        <v>0.004723224234076895</v>
       </c>
       <c r="AX22" t="n">
-        <v>118.7004075713254</v>
+        <v>0.3346859140599037</v>
       </c>
       <c r="AY22" t="n">
-        <v>-0.1373057669781588</v>
+        <v>0.05138833472068072</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.004723224234069789</v>
+        <v>0.2842223390619694</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.3346859140598895</v>
+        <v>-0.1379028279730647</v>
       </c>
       <c r="BB22" t="n">
-        <v>0.05138833472069138</v>
+        <v>0.973631473297786</v>
       </c>
       <c r="BC22" t="n">
-        <v>0.2842223390619694</v>
+        <v>0.08354745012648834</v>
       </c>
       <c r="BD22" t="n">
-        <v>-0.1379028279730647</v>
+        <v>0.6542144937718177</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.9736314732977718</v>
+        <v>-0.001394495050945466</v>
       </c>
       <c r="BF22" t="n">
-        <v>0.08354745012647413</v>
+        <v>55.78429448729583</v>
       </c>
       <c r="BG22" t="n">
-        <v>0.6542144937718177</v>
+        <v>64.46379373844189</v>
       </c>
       <c r="BH22" t="n">
-        <v>-0.001394495050973887</v>
+        <v>120.2033858454475</v>
       </c>
       <c r="BI22" t="n">
-        <v>0.7245872631347456</v>
+        <v>0.8660630045610223</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.1830346479076495</v>
+        <v>0.2133639466877231</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.852469069101268</v>
+        <v>2.014586478409578</v>
       </c>
       <c r="BL22" t="n">
-        <v>-0.1006913227605422</v>
+        <v>-0.04842225572576364</v>
       </c>
       <c r="BM22" t="n">
-        <v>6.118807028438709</v>
+        <v>6.188805154976656</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.276506258648711</v>
+        <v>1.300323635860943</v>
       </c>
     </row>
     <row r="23">
@@ -4968,43 +4968,43 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>319.4899902698842</v>
+        <v>101.0260032846573</v>
       </c>
       <c r="D23" t="n">
-        <v>16.68668706366356</v>
+        <v>16.68668706366357</v>
       </c>
       <c r="E23" t="n">
         <v>0.0169553542509675</v>
       </c>
       <c r="F23" t="n">
-        <v>320.3611098705454</v>
+        <v>101.3915375192115</v>
       </c>
       <c r="G23" t="n">
-        <v>22.42887781021442</v>
+        <v>22.42887781021443</v>
       </c>
       <c r="H23" t="n">
         <v>0.02963885106146336</v>
       </c>
       <c r="I23" t="n">
-        <v>318.3752519019106</v>
+        <v>100.7737760848187</v>
       </c>
       <c r="J23" t="n">
-        <v>3.957099102913062</v>
+        <v>3.957099102913065</v>
       </c>
       <c r="K23" t="n">
         <v>0.9806073009967804</v>
       </c>
       <c r="L23" t="n">
-        <v>315.7502965724215</v>
+        <v>96.96967348139336</v>
       </c>
       <c r="M23" t="n">
-        <v>5.971178095391451</v>
+        <v>5.971178095391457</v>
       </c>
       <c r="N23" t="n">
         <v>0.992126077413559</v>
       </c>
       <c r="O23" t="n">
-        <v>312.4578612916013</v>
+        <v>93.35358954490499</v>
       </c>
       <c r="P23" t="n">
         <v>15.00862608564661</v>
@@ -5013,16 +5013,16 @@
         <v>0.9525209367275238</v>
       </c>
       <c r="R23" t="n">
-        <v>318.8792468068448</v>
+        <v>101.0747316986957</v>
       </c>
       <c r="S23" t="n">
-        <v>18.7557058131441</v>
+        <v>18.75570581314412</v>
       </c>
       <c r="T23" t="n">
         <v>0.3907972276210785</v>
       </c>
       <c r="U23" t="n">
-        <v>314.5675108787862</v>
+        <v>96.28231144965963</v>
       </c>
       <c r="V23" t="n">
         <v>26.49816147824551</v>
@@ -5031,61 +5031,61 @@
         <v>0.6941878199577332</v>
       </c>
       <c r="X23" t="n">
-        <v>270.5842829765157</v>
+        <v>53.37995772666119</v>
       </c>
       <c r="Y23" t="n">
-        <v>21.36281601926115</v>
+        <v>21.36281601926114</v>
       </c>
       <c r="Z23" t="n">
         <v>0.966550350189209</v>
       </c>
       <c r="AA23" t="n">
-        <v>265.690929331678</v>
+        <v>48.59877241418718</v>
       </c>
       <c r="AB23" t="n">
-        <v>13.55503163439163</v>
+        <v>13.55503163439162</v>
       </c>
       <c r="AC23" t="n">
         <v>0.9839580357074738</v>
       </c>
       <c r="AD23" t="n">
-        <v>268.8094626081751</v>
+        <v>51.54475151224338</v>
       </c>
       <c r="AE23" t="n">
-        <v>4.800463737325472</v>
+        <v>4.800463737325465</v>
       </c>
       <c r="AF23" t="n">
         <v>0.9901006817817688</v>
       </c>
       <c r="AG23" t="n">
-        <v>256.6203584062292</v>
+        <v>38.81084360974899</v>
       </c>
       <c r="AH23" t="n">
-        <v>5.618643253407583</v>
+        <v>5.61864325340758</v>
       </c>
       <c r="AI23" t="n">
         <v>0.9980684816837311</v>
       </c>
       <c r="AJ23" t="n">
-        <v>260.7232986612523</v>
+        <v>42.81281613289042</v>
       </c>
       <c r="AK23" t="n">
-        <v>-2.049076810796208</v>
+        <v>-2.04907681079621</v>
       </c>
       <c r="AL23" t="n">
         <v>0.9985312521457672</v>
       </c>
       <c r="AM23" t="n">
-        <v>254.4241357356944</v>
+        <v>36.11822331205327</v>
       </c>
       <c r="AN23" t="n">
-        <v>13.81391971669298</v>
+        <v>13.81391971669299</v>
       </c>
       <c r="AO23" t="n">
         <v>0.9996904134750366</v>
       </c>
       <c r="AP23" t="n">
-        <v>226.6548521975254</v>
+        <v>9.224372214459365</v>
       </c>
       <c r="AQ23" t="n">
         <v>23.48322766892453</v>
@@ -5094,7 +5094,7 @@
         <v>0.9718672931194305</v>
       </c>
       <c r="AS23" t="n">
-        <v>200.1061784460189</v>
+        <v>-17.6635336368642</v>
       </c>
       <c r="AT23" t="n">
         <v>37.31815256970994</v>
@@ -5103,61 +5103,61 @@
         <v>0.9896596372127533</v>
       </c>
       <c r="AV23" t="n">
-        <v>58.03826092135939</v>
+        <v>-0.05393636987565742</v>
       </c>
       <c r="AW23" t="n">
-        <v>66.544826412015</v>
+        <v>0.07757176744176775</v>
       </c>
       <c r="AX23" t="n">
-        <v>128.3374589292698</v>
+        <v>0.5980653965726788</v>
       </c>
       <c r="AY23" t="n">
-        <v>-0.05393636987564321</v>
+        <v>-0.0678574785273014</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.07757176744176775</v>
+        <v>0.2190214522341591</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.5980653965726788</v>
+        <v>-0.03138755230192913</v>
       </c>
       <c r="BB23" t="n">
-        <v>-0.0678574785273014</v>
+        <v>0.9335406283114764</v>
       </c>
       <c r="BC23" t="n">
-        <v>0.2190214522341591</v>
+        <v>-0.05140761111645986</v>
       </c>
       <c r="BD23" t="n">
-        <v>-0.03138755230192203</v>
+        <v>1.237228068899597</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.9335406283114764</v>
+        <v>0.01273155212401633</v>
       </c>
       <c r="BF23" t="n">
-        <v>-0.05140761111645276</v>
+        <v>58.79280221307039</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.237228068899597</v>
+        <v>67.71668995766595</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.01273155212403765</v>
+        <v>129.9394028217002</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.110361853404997</v>
+        <v>2.235052120208627</v>
       </c>
       <c r="BJ23" t="n">
-        <v>-0.004378609407194034</v>
+        <v>-0.06135985497832763</v>
       </c>
       <c r="BK23" t="n">
-        <v>2.635879227833197</v>
+        <v>2.752485123990784</v>
       </c>
       <c r="BL23" t="n">
-        <v>1.229831425879293</v>
+        <v>1.160755757428344</v>
       </c>
       <c r="BM23" t="n">
-        <v>2.830311717071609</v>
+        <v>2.842380226864762</v>
       </c>
       <c r="BN23" t="n">
-        <v>-0.6029674888658967</v>
+        <v>-0.624459958720248</v>
       </c>
     </row>
     <row r="24">
@@ -5168,79 +5168,79 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>320.0257705564194</v>
+        <v>101.5617835711926</v>
       </c>
       <c r="D24" t="n">
-        <v>25.98497106673868</v>
+        <v>25.9849710667387</v>
       </c>
       <c r="E24" t="n">
         <v>0.01515860762447119</v>
       </c>
       <c r="F24" t="n">
-        <v>320.2092505832936</v>
+        <v>101.2396782319596</v>
       </c>
       <c r="G24" t="n">
-        <v>22.81261200600481</v>
+        <v>22.81261200600482</v>
       </c>
       <c r="H24" t="n">
         <v>0.02489517908543348</v>
       </c>
       <c r="I24" t="n">
-        <v>318.1784452910119</v>
+        <v>100.57696947392</v>
       </c>
       <c r="J24" t="n">
-        <v>4.399823127908903</v>
+        <v>4.39982312790891</v>
       </c>
       <c r="K24" t="n">
         <v>0.9869638979434967</v>
       </c>
       <c r="L24" t="n">
-        <v>316.0117760617682</v>
+        <v>97.23115297074014</v>
       </c>
       <c r="M24" t="n">
-        <v>6.285054632957937</v>
+        <v>6.285054632957946</v>
       </c>
       <c r="N24" t="n">
         <v>0.9900064468383789</v>
       </c>
       <c r="O24" t="n">
-        <v>313.3438886480129</v>
+        <v>94.23961690131654</v>
       </c>
       <c r="P24" t="n">
-        <v>15.23995906748669</v>
+        <v>15.2399590674867</v>
       </c>
       <c r="Q24" t="n">
         <v>0.8390500247478485</v>
       </c>
       <c r="R24" t="n">
-        <v>319.2510782404149</v>
+        <v>101.4465631322658</v>
       </c>
       <c r="S24" t="n">
-        <v>18.42072669495926</v>
+        <v>18.42072669495928</v>
       </c>
       <c r="T24" t="n">
         <v>0.2157099768519402</v>
       </c>
       <c r="U24" t="n">
-        <v>315.3943607147704</v>
+        <v>97.10916128564389</v>
       </c>
       <c r="V24" t="n">
-        <v>26.40411295789352</v>
+        <v>26.40411295789353</v>
       </c>
       <c r="W24" t="n">
         <v>0.6333348155021667</v>
       </c>
       <c r="X24" t="n">
-        <v>272.619111487206</v>
+        <v>55.41478623735142</v>
       </c>
       <c r="Y24" t="n">
-        <v>21.19057026315244</v>
+        <v>21.19057026315243</v>
       </c>
       <c r="Z24" t="n">
         <v>0.9664733111858368</v>
       </c>
       <c r="AA24" t="n">
-        <v>267.4765323070769</v>
+        <v>50.3843753895861</v>
       </c>
       <c r="AB24" t="n">
         <v>13.69028294340093</v>
@@ -5249,43 +5249,43 @@
         <v>0.9904689788818359</v>
       </c>
       <c r="AD24" t="n">
-        <v>269.1137151515231</v>
+        <v>51.84900405559134</v>
       </c>
       <c r="AE24" t="n">
-        <v>4.357252729699965</v>
+        <v>4.357252729699967</v>
       </c>
       <c r="AF24" t="n">
         <v>0.989160418510437</v>
       </c>
       <c r="AG24" t="n">
-        <v>257.3769488233202</v>
+        <v>39.56743402683989</v>
       </c>
       <c r="AH24" t="n">
-        <v>5.520118551051354</v>
+        <v>5.520118551051363</v>
       </c>
       <c r="AI24" t="n">
         <v>0.9986948370933533</v>
       </c>
       <c r="AJ24" t="n">
-        <v>260.783988871473</v>
+        <v>42.87350634311107</v>
       </c>
       <c r="AK24" t="n">
-        <v>-2.258617319959271</v>
+        <v>-2.258617319959275</v>
       </c>
       <c r="AL24" t="n">
         <v>0.9982322752475739</v>
       </c>
       <c r="AM24" t="n">
-        <v>256.5520347432887</v>
+        <v>38.24612231964761</v>
       </c>
       <c r="AN24" t="n">
-        <v>13.7351746254779</v>
+        <v>13.73517462547789</v>
       </c>
       <c r="AO24" t="n">
         <v>0.9995814263820648</v>
       </c>
       <c r="AP24" t="n">
-        <v>229.9179198894095</v>
+        <v>12.4874399063435</v>
       </c>
       <c r="AQ24" t="n">
         <v>21.8217078675615</v>
@@ -5294,7 +5294,7 @@
         <v>0.9663142561912537</v>
       </c>
       <c r="AS24" t="n">
-        <v>205.4901407120076</v>
+        <v>-12.27957137087559</v>
       </c>
       <c r="AT24" t="n">
         <v>33.40668779738407</v>
@@ -5303,61 +5303,61 @@
         <v>0.9940561056137085</v>
       </c>
       <c r="AV24" t="n">
-        <v>60.67924249862531</v>
+        <v>0.1095508007293091</v>
       </c>
       <c r="AW24" t="n">
-        <v>74.33521466820952</v>
+        <v>0.1084413934261264</v>
       </c>
       <c r="AX24" t="n">
-        <v>135.5626403317507</v>
+        <v>0.2600203169153161</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.1095508007293091</v>
+        <v>0.1133426706841547</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.1084413934261264</v>
+        <v>0.2234469068811222</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.2600203169153161</v>
+        <v>0.3993379308822327</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.1133426706841547</v>
+        <v>0.9858892319050199</v>
       </c>
       <c r="BC24" t="n">
-        <v>0.2234469068811364</v>
+        <v>0.2135286939905114</v>
       </c>
       <c r="BD24" t="n">
-        <v>0.3993379308822185</v>
+        <v>0.9070802242197971</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.9858892319050199</v>
+        <v>0.1738664951730371</v>
       </c>
       <c r="BF24" t="n">
-        <v>0.2135286939905114</v>
+        <v>61.55587051893163</v>
       </c>
       <c r="BG24" t="n">
-        <v>0.9070802242197828</v>
+        <v>75.61260920660339</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.1738664951730229</v>
+        <v>137.1775799630718</v>
       </c>
       <c r="BI24" t="n">
-        <v>-0.2913998198622743</v>
+        <v>-0.2131998253801566</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.1502056921810793</v>
+        <v>0.145066267150165</v>
       </c>
       <c r="BK24" t="n">
-        <v>2.865753343879735</v>
+        <v>2.945551788311111</v>
       </c>
       <c r="BL24" t="n">
-        <v>-1.666410004120777</v>
+        <v>-1.666990781828234</v>
       </c>
       <c r="BM24" t="n">
-        <v>5.083509028943205</v>
+        <v>5.083133457691758</v>
       </c>
       <c r="BN24" t="n">
-        <v>-0.7131749324851651</v>
+        <v>-0.7273698688660026</v>
       </c>
     </row>
     <row r="25">
@@ -5368,79 +5368,79 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>266.4527900675509</v>
+        <v>47.98880308232408</v>
       </c>
       <c r="D25" t="n">
-        <v>14.55775727616978</v>
+        <v>14.5577572761698</v>
       </c>
       <c r="E25" t="n">
         <v>0.01250892458483577</v>
       </c>
       <c r="F25" t="n">
-        <v>319.8001552769479</v>
+        <v>100.8305829256139</v>
       </c>
       <c r="G25" t="n">
-        <v>21.92112537140541</v>
+        <v>21.92112537140542</v>
       </c>
       <c r="H25" t="n">
         <v>0.01592230098322034</v>
       </c>
       <c r="I25" t="n">
-        <v>318.2565453204703</v>
+        <v>100.6550695033784</v>
       </c>
       <c r="J25" t="n">
-        <v>3.415558185983201</v>
+        <v>3.415558185983212</v>
       </c>
       <c r="K25" t="n">
         <v>0.9876768589019775</v>
       </c>
       <c r="L25" t="n">
-        <v>316.0727790061463</v>
+        <v>97.29215591511829</v>
       </c>
       <c r="M25" t="n">
-        <v>5.500501267453444</v>
+        <v>5.500501267453458</v>
       </c>
       <c r="N25" t="n">
         <v>0.9926529228687286</v>
       </c>
       <c r="O25" t="n">
-        <v>316.3729041180712</v>
+        <v>97.26863237137491</v>
       </c>
       <c r="P25" t="n">
-        <v>14.78931345838181</v>
+        <v>14.78931345838182</v>
       </c>
       <c r="Q25" t="n">
         <v>0.8446299433708191</v>
       </c>
       <c r="R25" t="n">
-        <v>319.7371887716841</v>
+        <v>101.932673663535</v>
       </c>
       <c r="S25" t="n">
-        <v>17.10077651003573</v>
+        <v>17.10077651003574</v>
       </c>
       <c r="T25" t="n">
         <v>0.120923176407814</v>
       </c>
       <c r="U25" t="n">
-        <v>317.4109783578426</v>
+        <v>99.12577892871613</v>
       </c>
       <c r="V25" t="n">
-        <v>25.07144035177026</v>
+        <v>25.07144035177028</v>
       </c>
       <c r="W25" t="n">
         <v>0.4902695417404175</v>
       </c>
       <c r="X25" t="n">
-        <v>275.3494059785884</v>
+        <v>58.1450807287338</v>
       </c>
       <c r="Y25" t="n">
-        <v>22.01628989361704</v>
+        <v>22.01628989361702</v>
       </c>
       <c r="Z25" t="n">
         <v>0.9761993288993835</v>
       </c>
       <c r="AA25" t="n">
-        <v>270.1162500584379</v>
+        <v>53.02409314094706</v>
       </c>
       <c r="AB25" t="n">
         <v>14.50963933417138</v>
@@ -5449,43 +5449,43 @@
         <v>0.9881750345230103</v>
       </c>
       <c r="AD25" t="n">
-        <v>271.0153194183999</v>
+        <v>53.75060832246822</v>
       </c>
       <c r="AE25" t="n">
-        <v>4.607326426404597</v>
+        <v>4.607326426404589</v>
       </c>
       <c r="AF25" t="n">
         <v>0.9935662448406219</v>
       </c>
       <c r="AG25" t="n">
-        <v>258.5869099231477</v>
+        <v>40.77739512666741</v>
       </c>
       <c r="AH25" t="n">
-        <v>6.648100183365202</v>
+        <v>6.648100183365193</v>
       </c>
       <c r="AI25" t="n">
         <v>0.9982907176017761</v>
       </c>
       <c r="AJ25" t="n">
-        <v>261.2784446553981</v>
+        <v>43.36796212703624</v>
       </c>
       <c r="AK25" t="n">
-        <v>-2.36229592181266</v>
+        <v>-2.362295921812667</v>
       </c>
       <c r="AL25" t="n">
         <v>0.9986506104469299</v>
       </c>
       <c r="AM25" t="n">
-        <v>258.8562336373836</v>
+        <v>40.55032121374251</v>
       </c>
       <c r="AN25" t="n">
-        <v>14.91117274507565</v>
+        <v>14.91117274507563</v>
       </c>
       <c r="AO25" t="n">
         <v>0.9997495412826538</v>
       </c>
       <c r="AP25" t="n">
-        <v>234.2312508441032</v>
+        <v>16.80077086103724</v>
       </c>
       <c r="AQ25" t="n">
         <v>18.7603808463888</v>
@@ -5494,70 +5494,70 @@
         <v>0.966382622718811</v>
       </c>
       <c r="AS25" t="n">
-        <v>211.6485920358211</v>
+        <v>-6.121120047062007</v>
       </c>
       <c r="AT25" t="n">
-        <v>26.28903490431766</v>
+        <v>26.28903490431765</v>
       </c>
       <c r="AU25" t="n">
         <v>0.9924890398979187</v>
       </c>
       <c r="AV25" t="n">
-        <v>63.92104684461555</v>
+        <v>0.3607019465020329</v>
       </c>
       <c r="AW25" t="n">
-        <v>75.45996290792093</v>
+        <v>0.1619085352471572</v>
       </c>
       <c r="AX25" t="n">
-        <v>139.9351220042909</v>
+        <v>1.427602767944336</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.3607019465020329</v>
+        <v>0.9643823542493593</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.1619085352471501</v>
+        <v>1.744474248683204</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.427602767944336</v>
+        <v>0.5697585166768704</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.9643823542493593</v>
+        <v>1.512739506173645</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.74447424868319</v>
+        <v>0.07560253143310547</v>
       </c>
       <c r="BD25" t="n">
-        <v>0.5697585166768846</v>
+        <v>1.692552769437754</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.512739506173645</v>
+        <v>0.05068220990768424</v>
       </c>
       <c r="BF25" t="n">
-        <v>0.07560253143310547</v>
+        <v>64.89920389339353</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.692552769437754</v>
+        <v>76.8405653282279</v>
       </c>
       <c r="BH25" t="n">
-        <v>0.05068220990769134</v>
+        <v>141.5062776289794</v>
       </c>
       <c r="BI25" t="n">
-        <v>7.321297541374394</v>
+        <v>7.308705858917483</v>
       </c>
       <c r="BJ25" t="n">
-        <v>4.567113658517834</v>
+        <v>4.551768534049808</v>
       </c>
       <c r="BK25" t="n">
-        <v>-1.324258252318593</v>
+        <v>-1.34604417273713</v>
       </c>
       <c r="BL25" t="n">
-        <v>-2.421226947108225</v>
+        <v>-2.430755495102057</v>
       </c>
       <c r="BM25" t="n">
-        <v>-2.463887702593198</v>
+        <v>-2.491253427275453</v>
       </c>
       <c r="BN25" t="n">
-        <v>-2.850709295635529</v>
+        <v>-2.844886609016346</v>
       </c>
     </row>
     <row r="26">
@@ -5568,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>216.8852866964137</v>
+        <v>-1.578700288813167</v>
       </c>
       <c r="D26" t="n">
         <v>24.3974969742146</v>
@@ -5577,34 +5577,34 @@
         <v>0.02305431570857763</v>
       </c>
       <c r="F26" t="n">
-        <v>268.1863975334675</v>
+        <v>49.21682518213353</v>
       </c>
       <c r="G26" t="n">
-        <v>23.09021645403922</v>
+        <v>23.09021645403923</v>
       </c>
       <c r="H26" t="n">
         <v>0.008331781253218651</v>
       </c>
       <c r="I26" t="n">
-        <v>318.1551626388062</v>
+        <v>100.5536868217144</v>
       </c>
       <c r="J26" t="n">
-        <v>3.167140230219417</v>
+        <v>3.167140230219415</v>
       </c>
       <c r="K26" t="n">
         <v>0.9892102479934692</v>
       </c>
       <c r="L26" t="n">
-        <v>316.2619968678089</v>
+        <v>97.4813737767808</v>
       </c>
       <c r="M26" t="n">
-        <v>5.563281444793063</v>
+        <v>5.563281444793052</v>
       </c>
       <c r="N26" t="n">
         <v>0.9919496476650238</v>
       </c>
       <c r="O26" t="n">
-        <v>317.9618206429989</v>
+        <v>98.85754889630257</v>
       </c>
       <c r="P26" t="n">
         <v>14.73861856663481</v>
@@ -5613,7 +5613,7 @@
         <v>0.8435651957988739</v>
       </c>
       <c r="R26" t="n">
-        <v>319.5626323527479</v>
+        <v>101.7581172445987</v>
       </c>
       <c r="S26" t="n">
         <v>18.87472436783162</v>
@@ -5622,16 +5622,16 @@
         <v>0.05312108807265759</v>
       </c>
       <c r="U26" t="n">
-        <v>318.5667698053604</v>
+        <v>100.2815703762339</v>
       </c>
       <c r="V26" t="n">
-        <v>24.58403567050367</v>
+        <v>24.58403567050366</v>
       </c>
       <c r="W26" t="n">
         <v>0.419769823551178</v>
       </c>
       <c r="X26" t="n">
-        <v>278.2824293096015</v>
+        <v>61.07810405974692</v>
       </c>
       <c r="Y26" t="n">
         <v>23.62321894219581</v>
@@ -5640,124 +5640,124 @@
         <v>0.9790649712085724</v>
       </c>
       <c r="AA26" t="n">
-        <v>273.0583779355313</v>
+        <v>55.96622101804044</v>
       </c>
       <c r="AB26" t="n">
-        <v>16.08746305425116</v>
+        <v>16.08746305425117</v>
       </c>
       <c r="AC26" t="n">
         <v>0.990422785282135</v>
       </c>
       <c r="AD26" t="n">
-        <v>275.1959577519843</v>
+        <v>57.93124665605259</v>
       </c>
       <c r="AE26" t="n">
-        <v>6.352323166867507</v>
+        <v>6.352323166867521</v>
       </c>
       <c r="AF26" t="n">
         <v>0.9923641085624695</v>
       </c>
       <c r="AG26" t="n">
-        <v>263.6544004399726</v>
+        <v>45.84488564349238</v>
       </c>
       <c r="AH26" t="n">
-        <v>8.530588352933833</v>
+        <v>8.530588352933844</v>
       </c>
       <c r="AI26" t="n">
         <v>0.9983869194984436</v>
       </c>
       <c r="AJ26" t="n">
-        <v>262.4205345803119</v>
+        <v>44.51005205195003</v>
       </c>
       <c r="AK26" t="n">
-        <v>-1.933946000768799</v>
+        <v>-1.933946000768783</v>
       </c>
       <c r="AL26" t="n">
         <v>0.999021053314209</v>
       </c>
       <c r="AM26" t="n">
-        <v>261.5290641784668</v>
+        <v>43.22315175482566</v>
       </c>
       <c r="AN26" t="n">
-        <v>16.48327441925697</v>
+        <v>16.48327441925698</v>
       </c>
       <c r="AO26" t="n">
         <v>0.9990198910236359</v>
       </c>
       <c r="AP26" t="n">
-        <v>238.1669551768202</v>
+        <v>20.73647519375415</v>
       </c>
       <c r="AQ26" t="n">
-        <v>19.39131554136884</v>
+        <v>19.39131554136885</v>
       </c>
       <c r="AR26" t="n">
         <v>0.9444967806339264</v>
       </c>
       <c r="AS26" t="n">
-        <v>215.5184684915745</v>
+        <v>-2.251243591308608</v>
       </c>
       <c r="AT26" t="n">
-        <v>22.62557009433176</v>
+        <v>22.62557009433178</v>
       </c>
       <c r="AU26" t="n">
         <v>0.9897323250770569</v>
       </c>
       <c r="AV26" t="n">
-        <v>85.43130582467712</v>
+        <v>0.9847569972910861</v>
       </c>
       <c r="AW26" t="n">
-        <v>66.89980335919942</v>
+        <v>0.4342515417869919</v>
       </c>
       <c r="AX26" t="n">
-        <v>132.904766494289</v>
+        <v>3.454363599736652</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.9847569972910719</v>
+        <v>0.7790301708464824</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.4342515417870061</v>
+        <v>2.624077492571871</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.454363599736652</v>
+        <v>0.649684033495312</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.7790301708464824</v>
+        <v>1.816125626259677</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.624077492571914</v>
+        <v>0.4880945733253128</v>
       </c>
       <c r="BD26" t="n">
-        <v>0.6496840334953404</v>
+        <v>1.588704738211121</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.816125626259677</v>
+        <v>0.3213593300352784</v>
       </c>
       <c r="BF26" t="n">
-        <v>0.4880945733253128</v>
+        <v>86.44961140405466</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.588704738211121</v>
+        <v>68.34549946944418</v>
       </c>
       <c r="BH26" t="n">
-        <v>0.3213593300352784</v>
+        <v>134.4554288588217</v>
       </c>
       <c r="BI26" t="n">
-        <v>10.44329491090748</v>
+        <v>10.49974941311887</v>
       </c>
       <c r="BJ26" t="n">
-        <v>-0.7405664376818164</v>
+        <v>-0.7303588712591464</v>
       </c>
       <c r="BK26" t="n">
-        <v>-7.168036022156381</v>
+        <v>-7.052181612039419</v>
       </c>
       <c r="BL26" t="n">
-        <v>-2.296046967546694</v>
+        <v>-2.241300919480084</v>
       </c>
       <c r="BM26" t="n">
-        <v>-3.198743843751217</v>
+        <v>-3.203422307355716</v>
       </c>
       <c r="BN26" t="n">
-        <v>-0.06017425674800592</v>
+        <v>-0.06177116511507208</v>
       </c>
     </row>
   </sheetData>
